--- a/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C883DEB-3E82-42D9-A9ED-D71BF949B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD258453-968A-46A8-B218-CE31F8692284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,9 @@
     <t>42761010,42663010</t>
   </si>
   <si>
+    <t>42652007</t>
+  </si>
+  <si>
     <t>drop_exp_num</t>
   </si>
   <si>
@@ -126,10 +129,28 @@
     <t>46700001:5</t>
   </si>
   <si>
+    <t>42761001</t>
+  </si>
+  <si>
+    <t>42663002</t>
+  </si>
+  <si>
+    <t>42761003</t>
+  </si>
+  <si>
     <t>46700001:6</t>
   </si>
   <si>
+    <t>42663004</t>
+  </si>
+  <si>
     <t>46700001:7</t>
+  </si>
+  <si>
+    <t>42655004</t>
+  </si>
+  <si>
+    <t>42761005</t>
   </si>
   <si>
     <t>46700001:12</t>
@@ -141,13 +162,25 @@
     <t>46200001:60</t>
   </si>
   <si>
+    <t>42663006</t>
+  </si>
+  <si>
     <t>46700001:13</t>
+  </si>
+  <si>
+    <t>42657006</t>
   </si>
   <si>
     <t>46700001:10</t>
   </si>
   <si>
     <t>46200001:80</t>
+  </si>
+  <si>
+    <t>42664006</t>
+  </si>
+  <si>
+    <t>42761007</t>
   </si>
   <si>
     <t>46700001:17</t>
@@ -160,6 +193,9 @@
   </si>
   <si>
     <t>46200001:120</t>
+  </si>
+  <si>
+    <t>42668007</t>
   </si>
   <si>
     <t>46700001:18</t>
@@ -528,19 +564,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -557,10 +593,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -577,10 +613,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -590,14 +626,14 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -611,10 +647,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -624,14 +660,14 @@
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2">
-        <v>0</v>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -645,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -658,14 +694,14 @@
       <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="2">
-        <v>0</v>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -679,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -692,14 +728,14 @@
       <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -713,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -726,14 +762,14 @@
       <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -743,14 +779,14 @@
       <c r="B14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
+      <c r="D14" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -764,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -781,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -798,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
@@ -811,14 +847,14 @@
       <c r="B18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
+      <c r="D18" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -832,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -845,14 +881,14 @@
       <c r="B20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -866,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -883,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -896,14 +932,14 @@
       <c r="B23" s="1">
         <v>6</v>
       </c>
-      <c r="D23" s="2">
-        <v>0</v>
+      <c r="D23" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -917,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -930,14 +966,14 @@
       <c r="B25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="2">
-        <v>0</v>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -951,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -968,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -981,14 +1017,14 @@
       <c r="B28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="2">
-        <v>0</v>
+      <c r="D28" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
@@ -1002,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1019,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1032,14 +1068,14 @@
       <c r="B31" s="1">
         <v>7</v>
       </c>
-      <c r="D31" s="2">
-        <v>0</v>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1053,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1070,10 +1106,10 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1087,10 +1123,10 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1104,10 +1140,10 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1121,10 +1157,10 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1138,10 +1174,10 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1155,10 +1191,10 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1172,10 +1208,10 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1189,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
@@ -1206,10 +1242,10 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1223,10 +1259,10 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1240,10 +1276,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1257,10 +1293,10 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1274,10 +1310,10 @@
         <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1291,10 +1327,10 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1308,10 +1344,10 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1325,10 +1361,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1342,10 +1378,10 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -1359,10 +1395,10 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -1376,10 +1412,10 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
@@ -1393,10 +1429,10 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -1410,10 +1446,10 @@
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -1427,10 +1463,10 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -1444,10 +1480,10 @@
         <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -1461,10 +1497,10 @@
         <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -1478,10 +1514,10 @@
         <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -1495,10 +1531,10 @@
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -1512,10 +1548,10 @@
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -1529,10 +1565,10 @@
         <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -1546,10 +1582,10 @@
         <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
@@ -1563,10 +1599,10 @@
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
@@ -1580,10 +1616,10 @@
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -1597,10 +1633,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -1614,10 +1650,10 @@
         <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -1631,10 +1667,10 @@
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -1648,10 +1684,10 @@
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -1665,10 +1701,10 @@
         <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -1682,10 +1718,10 @@
         <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -1699,10 +1735,10 @@
         <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -1716,10 +1752,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -1733,10 +1769,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -1750,10 +1786,10 @@
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -1767,10 +1803,10 @@
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -1784,10 +1820,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -1801,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -1818,10 +1854,10 @@
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -1835,10 +1871,10 @@
         <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -1852,10 +1888,10 @@
         <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -1869,10 +1905,10 @@
         <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -1886,10 +1922,10 @@
         <v>11</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -1903,10 +1939,10 @@
         <v>11</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -1920,10 +1956,10 @@
         <v>11</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
@@ -1937,10 +1973,10 @@
         <v>11</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -1954,10 +1990,10 @@
         <v>11</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -1971,10 +2007,10 @@
         <v>11</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -1988,10 +2024,10 @@
         <v>11</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2005,10 +2041,10 @@
         <v>11</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2022,10 +2058,10 @@
         <v>11</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2039,10 +2075,10 @@
         <v>11</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2056,10 +2092,10 @@
         <v>11</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2073,10 +2109,10 @@
         <v>11</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2090,10 +2126,10 @@
         <v>11</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2107,10 +2143,10 @@
         <v>11</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2124,10 +2160,10 @@
         <v>11</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2141,10 +2177,10 @@
         <v>11</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
@@ -2158,10 +2194,10 @@
         <v>11</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2175,10 +2211,10 @@
         <v>11</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
@@ -2192,10 +2228,10 @@
         <v>11</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
@@ -2209,10 +2245,10 @@
         <v>11</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
@@ -2226,10 +2262,10 @@
         <v>11</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
@@ -2243,10 +2279,10 @@
         <v>11</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
@@ -2260,10 +2296,10 @@
         <v>11</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
@@ -2277,10 +2313,10 @@
         <v>11</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
@@ -2294,10 +2330,10 @@
         <v>11</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
@@ -2311,10 +2347,10 @@
         <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
@@ -2328,10 +2364,10 @@
         <v>11</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
@@ -2345,10 +2381,10 @@
         <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
@@ -2362,10 +2398,10 @@
         <v>11</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
@@ -2379,10 +2415,10 @@
         <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
@@ -2396,10 +2432,10 @@
         <v>11</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
@@ -2413,10 +2449,10 @@
         <v>11</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
@@ -2430,10 +2466,10 @@
         <v>11</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
@@ -2447,10 +2483,10 @@
         <v>11</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
@@ -2464,10 +2500,10 @@
         <v>11</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
@@ -2481,10 +2517,10 @@
         <v>11</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
@@ -2498,10 +2534,10 @@
         <v>11</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
@@ -2515,10 +2551,10 @@
         <v>11</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
@@ -2532,10 +2568,10 @@
         <v>11</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -2549,10 +2585,10 @@
         <v>11</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
@@ -2566,10 +2602,10 @@
         <v>11</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.15">
@@ -2583,10 +2619,10 @@
         <v>11</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.15">
@@ -2600,10 +2636,10 @@
         <v>11</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.15">
@@ -2617,10 +2653,10 @@
         <v>11</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.15">
@@ -2634,10 +2670,10 @@
         <v>11</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.15">
@@ -2651,10 +2687,10 @@
         <v>11</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.15">
@@ -2668,10 +2704,10 @@
         <v>11</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.15">
@@ -2685,10 +2721,10 @@
         <v>11</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.15">
@@ -2702,10 +2738,10 @@
         <v>11</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.15">
@@ -2719,10 +2755,10 @@
         <v>11</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -2736,10 +2772,10 @@
         <v>11</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -2753,10 +2789,10 @@
         <v>11</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
@@ -2770,10 +2806,10 @@
         <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
@@ -2787,10 +2823,10 @@
         <v>11</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
@@ -2804,10 +2840,10 @@
         <v>11</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
@@ -2821,10 +2857,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
@@ -2838,10 +2874,10 @@
         <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -2855,10 +2891,10 @@
         <v>11</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
@@ -2872,10 +2908,10 @@
         <v>11</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">
@@ -2889,10 +2925,10 @@
         <v>11</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
@@ -2906,10 +2942,10 @@
         <v>11</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -2923,10 +2959,10 @@
         <v>11</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -2940,10 +2976,10 @@
         <v>11</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -2957,10 +2993,10 @@
         <v>11</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
@@ -2974,10 +3010,10 @@
         <v>11</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
@@ -2991,10 +3027,10 @@
         <v>11</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
@@ -3008,10 +3044,10 @@
         <v>11</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
@@ -3025,10 +3061,10 @@
         <v>11</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
@@ -3042,10 +3078,10 @@
         <v>11</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
@@ -3059,10 +3095,10 @@
         <v>11</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
@@ -3076,10 +3112,10 @@
         <v>11</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.15">
@@ -3093,10 +3129,10 @@
         <v>11</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
@@ -3110,10 +3146,10 @@
         <v>11</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
@@ -3127,10 +3163,10 @@
         <v>11</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
@@ -3144,10 +3180,10 @@
         <v>11</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
@@ -3161,10 +3197,10 @@
         <v>11</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
@@ -3178,10 +3214,10 @@
         <v>11</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
@@ -3195,10 +3231,10 @@
         <v>11</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
@@ -3212,10 +3248,10 @@
         <v>11</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
@@ -3229,10 +3265,10 @@
         <v>11</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
@@ -3246,10 +3282,10 @@
         <v>11</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
@@ -3263,10 +3299,10 @@
         <v>11</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
@@ -3280,10 +3316,10 @@
         <v>11</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
@@ -3297,10 +3333,10 @@
         <v>11</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
@@ -3314,10 +3350,10 @@
         <v>11</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
@@ -3331,10 +3367,10 @@
         <v>11</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -3348,10 +3384,10 @@
         <v>11</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -3365,10 +3401,10 @@
         <v>11</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
@@ -3382,10 +3418,10 @@
         <v>11</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
@@ -3399,10 +3435,10 @@
         <v>11</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
@@ -3416,10 +3452,10 @@
         <v>11</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
@@ -3433,10 +3469,10 @@
         <v>11</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
@@ -3450,10 +3486,10 @@
         <v>11</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
@@ -3467,10 +3503,10 @@
         <v>11</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
@@ -3484,10 +3520,10 @@
         <v>11</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
@@ -3501,10 +3537,10 @@
         <v>11</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
@@ -3518,10 +3554,10 @@
         <v>11</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
@@ -3535,10 +3571,10 @@
         <v>11</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
@@ -3552,10 +3588,10 @@
         <v>11</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
@@ -3569,10 +3605,10 @@
         <v>11</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
@@ -3586,10 +3622,10 @@
         <v>11</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
@@ -3603,10 +3639,10 @@
         <v>11</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
@@ -3620,10 +3656,10 @@
         <v>11</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
@@ -3637,10 +3673,10 @@
         <v>11</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
@@ -3654,10 +3690,10 @@
         <v>11</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
@@ -3671,10 +3707,10 @@
         <v>11</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
@@ -3688,10 +3724,10 @@
         <v>11</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
@@ -3705,10 +3741,10 @@
         <v>11</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
@@ -3722,10 +3758,10 @@
         <v>11</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
@@ -3739,10 +3775,10 @@
         <v>11</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
@@ -3756,10 +3792,10 @@
         <v>11</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
@@ -3773,10 +3809,10 @@
         <v>11</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
@@ -3790,10 +3826,10 @@
         <v>11</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
@@ -3807,10 +3843,10 @@
         <v>11</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
@@ -3824,10 +3860,10 @@
         <v>11</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
@@ -3841,10 +3877,10 @@
         <v>11</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
@@ -3858,10 +3894,10 @@
         <v>11</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
@@ -3875,10 +3911,10 @@
         <v>11</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
@@ -3892,10 +3928,10 @@
         <v>11</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
@@ -3909,10 +3945,10 @@
         <v>11</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
@@ -3926,10 +3962,10 @@
         <v>11</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
@@ -3943,10 +3979,10 @@
         <v>11</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
@@ -3960,10 +3996,10 @@
         <v>11</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
@@ -3977,10 +4013,10 @@
         <v>11</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
@@ -3994,10 +4030,10 @@
         <v>11</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
@@ -4011,10 +4047,10 @@
         <v>11</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
@@ -4028,10 +4064,10 @@
         <v>11</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
@@ -4045,10 +4081,10 @@
         <v>11</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
@@ -4062,10 +4098,10 @@
         <v>11</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -4079,10 +4115,10 @@
         <v>11</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
@@ -4096,10 +4132,10 @@
         <v>11</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
@@ -4113,10 +4149,10 @@
         <v>11</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
@@ -4130,10 +4166,10 @@
         <v>11</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
@@ -4147,10 +4183,10 @@
         <v>11</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
@@ -4164,10 +4200,10 @@
         <v>11</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
@@ -4181,10 +4217,10 @@
         <v>11</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
@@ -4198,10 +4234,10 @@
         <v>11</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
@@ -4215,10 +4251,10 @@
         <v>11</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
@@ -4232,10 +4268,10 @@
         <v>11</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
@@ -4249,10 +4285,10 @@
         <v>11</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
@@ -4266,10 +4302,10 @@
         <v>11</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
@@ -4283,10 +4319,10 @@
         <v>11</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
@@ -4300,10 +4336,10 @@
         <v>11</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
@@ -4317,10 +4353,10 @@
         <v>11</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
@@ -4334,10 +4370,10 @@
         <v>11</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
@@ -4351,10 +4387,10 @@
         <v>11</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
@@ -4368,10 +4404,10 @@
         <v>11</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
@@ -4385,10 +4421,10 @@
         <v>11</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
@@ -4402,10 +4438,10 @@
         <v>11</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
@@ -4419,10 +4455,10 @@
         <v>11</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
@@ -4436,10 +4472,10 @@
         <v>11</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
@@ -4453,10 +4489,10 @@
         <v>11</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
@@ -4470,10 +4506,10 @@
         <v>11</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
@@ -4487,10 +4523,10 @@
         <v>11</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
@@ -4504,10 +4540,10 @@
         <v>11</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
@@ -4521,10 +4557,10 @@
         <v>11</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
@@ -4538,10 +4574,10 @@
         <v>11</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
@@ -4555,10 +4591,10 @@
         <v>11</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
@@ -4572,10 +4608,10 @@
         <v>11</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
@@ -4589,10 +4625,10 @@
         <v>11</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
@@ -4606,10 +4642,10 @@
         <v>11</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
@@ -4623,10 +4659,10 @@
         <v>11</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
@@ -4640,10 +4676,10 @@
         <v>11</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
@@ -4657,10 +4693,10 @@
         <v>11</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
@@ -4674,10 +4710,10 @@
         <v>11</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
@@ -4691,10 +4727,10 @@
         <v>11</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
@@ -4708,10 +4744,10 @@
         <v>11</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
@@ -4725,10 +4761,10 @@
         <v>11</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
@@ -4742,10 +4778,10 @@
         <v>11</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
@@ -4759,10 +4795,10 @@
         <v>11</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.15">
@@ -4776,10 +4812,10 @@
         <v>11</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.15">
@@ -4793,10 +4829,10 @@
         <v>11</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.15">
@@ -4810,10 +4846,10 @@
         <v>11</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.15">
@@ -4827,10 +4863,10 @@
         <v>11</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.15">
@@ -4844,10 +4880,10 @@
         <v>11</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.15">
@@ -4861,10 +4897,10 @@
         <v>11</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.15">
@@ -4878,10 +4914,10 @@
         <v>11</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.15">
@@ -4895,10 +4931,10 @@
         <v>11</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.15">
@@ -4912,10 +4948,10 @@
         <v>11</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.15">
@@ -4929,10 +4965,10 @@
         <v>11</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.15">
@@ -4946,10 +4982,10 @@
         <v>11</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.15">
@@ -4963,10 +4999,10 @@
         <v>11</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.15">
@@ -4980,10 +5016,10 @@
         <v>11</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.15">
@@ -4997,10 +5033,10 @@
         <v>11</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.15">
@@ -5014,10 +5050,10 @@
         <v>11</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.15">
@@ -5031,10 +5067,10 @@
         <v>11</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.15">
@@ -5048,10 +5084,10 @@
         <v>11</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.15">
@@ -5065,10 +5101,10 @@
         <v>11</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.15">
@@ -5082,10 +5118,10 @@
         <v>11</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.15">
@@ -5099,10 +5135,10 @@
         <v>11</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.15">
@@ -5116,10 +5152,10 @@
         <v>11</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.15">
@@ -5133,10 +5169,10 @@
         <v>11</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.15">
@@ -5150,10 +5186,10 @@
         <v>11</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.15">
@@ -5167,10 +5203,10 @@
         <v>11</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.15">
@@ -5184,10 +5220,10 @@
         <v>11</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.15">
@@ -5201,10 +5237,10 @@
         <v>11</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.15">
@@ -5218,10 +5254,10 @@
         <v>11</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.15">
@@ -5235,10 +5271,10 @@
         <v>11</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.15">
@@ -5252,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.15">
@@ -5269,10 +5305,10 @@
         <v>11</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.15">
@@ -5286,10 +5322,10 @@
         <v>11</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.15">
@@ -5303,10 +5339,10 @@
         <v>11</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.15">
@@ -5320,10 +5356,10 @@
         <v>11</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.15">
@@ -5337,10 +5373,10 @@
         <v>11</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.15">
@@ -5354,10 +5390,10 @@
         <v>11</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.15">
@@ -5371,10 +5407,10 @@
         <v>11</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.15">
@@ -5388,10 +5424,10 @@
         <v>11</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.15">
@@ -5405,10 +5441,10 @@
         <v>11</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.15">
@@ -5422,10 +5458,10 @@
         <v>11</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.15">
@@ -5439,10 +5475,10 @@
         <v>11</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.15">
@@ -5456,10 +5492,10 @@
         <v>11</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.15">
@@ -5473,10 +5509,10 @@
         <v>11</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.15">
@@ -5490,10 +5526,10 @@
         <v>11</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.15">
@@ -5507,10 +5543,10 @@
         <v>11</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.15">
@@ -5524,10 +5560,10 @@
         <v>11</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.15">
@@ -5541,10 +5577,10 @@
         <v>11</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.15">
@@ -5558,10 +5594,10 @@
         <v>11</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.15">
@@ -5575,10 +5611,10 @@
         <v>11</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.15">
@@ -5592,10 +5628,10 @@
         <v>11</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.15">
@@ -5609,10 +5645,10 @@
         <v>11</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.15">
@@ -5626,10 +5662,10 @@
         <v>11</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.15">
@@ -5643,10 +5679,10 @@
         <v>11</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.15">
@@ -5660,10 +5696,10 @@
         <v>11</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.15">
@@ -5677,10 +5713,10 @@
         <v>11</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.15">
@@ -5694,10 +5730,10 @@
         <v>11</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.15">
@@ -5711,10 +5747,10 @@
         <v>11</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.15">
@@ -5728,10 +5764,10 @@
         <v>11</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.15">
@@ -5745,10 +5781,10 @@
         <v>11</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.15">
@@ -5762,10 +5798,10 @@
         <v>11</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.15">
@@ -5779,10 +5815,10 @@
         <v>11</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.15">
@@ -5796,10 +5832,10 @@
         <v>11</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.15">
@@ -5813,10 +5849,10 @@
         <v>11</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.15">
@@ -5830,10 +5866,10 @@
         <v>11</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.15">
@@ -5847,10 +5883,10 @@
         <v>11</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.15">
@@ -5864,10 +5900,10 @@
         <v>11</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.15">
@@ -5881,10 +5917,10 @@
         <v>11</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.15">
@@ -5898,10 +5934,10 @@
         <v>11</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.15">
@@ -5915,10 +5951,10 @@
         <v>11</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.15">
@@ -5932,10 +5968,10 @@
         <v>11</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.15">
@@ -5949,10 +5985,10 @@
         <v>11</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.15">
@@ -5966,10 +6002,10 @@
         <v>11</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.15">
@@ -5983,10 +6019,10 @@
         <v>11</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.15">
@@ -6000,10 +6036,10 @@
         <v>11</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.15">
@@ -6017,10 +6053,10 @@
         <v>11</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.15">
@@ -6034,10 +6070,10 @@
         <v>11</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.15">
@@ -6051,10 +6087,10 @@
         <v>11</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.15">
@@ -6068,10 +6104,10 @@
         <v>11</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.15">
@@ -6085,10 +6121,10 @@
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.15">
@@ -6102,10 +6138,10 @@
         <v>11</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.15">
@@ -6119,10 +6155,10 @@
         <v>11</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.15">
@@ -6136,10 +6172,10 @@
         <v>11</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.15">
@@ -6153,10 +6189,10 @@
         <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.15">
@@ -6170,10 +6206,10 @@
         <v>11</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.15">
@@ -6187,10 +6223,10 @@
         <v>11</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.15">
@@ -6204,10 +6240,10 @@
         <v>11</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.15">
@@ -6221,10 +6257,10 @@
         <v>11</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.15">
@@ -6238,10 +6274,10 @@
         <v>11</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.15">
@@ -6255,10 +6291,10 @@
         <v>11</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F338" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.15">
@@ -6272,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.15">
@@ -6289,10 +6325,10 @@
         <v>0</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.15">
@@ -6306,10 +6342,10 @@
         <v>0</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.15">
@@ -6323,10 +6359,10 @@
         <v>0</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.15">
@@ -6340,10 +6376,10 @@
         <v>0</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.15">
@@ -6357,10 +6393,10 @@
         <v>0</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.15">
@@ -6374,10 +6410,10 @@
         <v>0</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.15">
@@ -6391,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.15">
@@ -6408,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.15">
@@ -6425,10 +6461,10 @@
         <v>0</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.15">
@@ -6442,10 +6478,10 @@
         <v>0</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.15">
@@ -6459,10 +6495,10 @@
         <v>0</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.15">
@@ -6476,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.15">
@@ -6493,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.15">
@@ -6510,10 +6546,10 @@
         <v>0</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.15">
@@ -6527,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.15">
@@ -6544,10 +6580,10 @@
         <v>0</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.15">
@@ -6561,10 +6597,10 @@
         <v>0</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.15">
@@ -6578,10 +6614,10 @@
         <v>0</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.15">
@@ -6595,10 +6631,10 @@
         <v>0</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.15">
@@ -6612,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.15">
@@ -6629,10 +6665,10 @@
         <v>0</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.15">
@@ -6646,10 +6682,10 @@
         <v>0</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.15">
@@ -6663,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.15">
@@ -6680,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.15">
@@ -6697,10 +6733,10 @@
         <v>0</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.15">
@@ -6714,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.15">
@@ -6731,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.15">
@@ -6748,10 +6784,10 @@
         <v>0</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.15">
@@ -6765,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.15">
@@ -6782,10 +6818,10 @@
         <v>0</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.15">
@@ -6799,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.15">
@@ -6816,10 +6852,10 @@
         <v>0</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.15">
@@ -6833,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.15">
@@ -6850,10 +6886,10 @@
         <v>0</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.15">
@@ -6867,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.15">
@@ -6884,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.15">
@@ -6901,10 +6937,10 @@
         <v>0</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.15">
@@ -6918,10 +6954,10 @@
         <v>0</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.15">
@@ -6935,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.15">
@@ -6952,10 +6988,10 @@
         <v>0</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.15">
@@ -6969,10 +7005,10 @@
         <v>0</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.15">
@@ -6986,10 +7022,10 @@
         <v>0</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.15">
@@ -7003,10 +7039,10 @@
         <v>0</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.15">
@@ -7020,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.15">
@@ -7037,10 +7073,10 @@
         <v>0</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.15">
@@ -7054,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.15">
@@ -7071,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.15">
@@ -7088,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.15">
@@ -7105,10 +7141,10 @@
         <v>0</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.15">
@@ -7122,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.15">
@@ -7139,10 +7175,10 @@
         <v>0</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.15">
@@ -7156,10 +7192,10 @@
         <v>0</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.15">
@@ -7173,10 +7209,10 @@
         <v>0</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.15">
@@ -7190,10 +7226,10 @@
         <v>0</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.15">
@@ -7207,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.15">
@@ -7224,10 +7260,10 @@
         <v>0</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.15">
@@ -7241,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.15">
@@ -7258,10 +7294,10 @@
         <v>0</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.15">
@@ -7275,10 +7311,10 @@
         <v>0</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.15">
@@ -7292,10 +7328,10 @@
         <v>0</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.15">
@@ -7309,10 +7345,10 @@
         <v>0</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.15">
@@ -7326,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.15">
@@ -7343,10 +7379,10 @@
         <v>0</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.15">
@@ -7360,10 +7396,10 @@
         <v>0</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.15">
@@ -7377,10 +7413,10 @@
         <v>0</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.15">
@@ -7394,10 +7430,10 @@
         <v>0</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.15">
@@ -7411,10 +7447,10 @@
         <v>0</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.15">
@@ -7428,10 +7464,10 @@
         <v>0</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.15">
@@ -7445,10 +7481,10 @@
         <v>0</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.15">
@@ -7462,10 +7498,10 @@
         <v>0</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.15">
@@ -7479,10 +7515,10 @@
         <v>0</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.15">
@@ -7496,10 +7532,10 @@
         <v>0</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.15">
@@ -7513,10 +7549,10 @@
         <v>0</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.15">
@@ -7530,10 +7566,10 @@
         <v>0</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.15">
@@ -7547,10 +7583,10 @@
         <v>0</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.15">
@@ -7564,10 +7600,10 @@
         <v>0</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.15">
@@ -7581,10 +7617,10 @@
         <v>0</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.15">
@@ -7598,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.15">
@@ -7615,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.15">
@@ -7632,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.15">
@@ -7649,10 +7685,10 @@
         <v>0</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.15">
@@ -7666,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.15">
@@ -7683,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.15">
@@ -7700,10 +7736,10 @@
         <v>0</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.15">
@@ -7717,10 +7753,10 @@
         <v>0</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.15">
@@ -7734,10 +7770,10 @@
         <v>0</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.15">
@@ -7751,10 +7787,10 @@
         <v>0</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.15">
@@ -7768,10 +7804,10 @@
         <v>0</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.15">
@@ -7785,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.15">
@@ -7802,10 +7838,10 @@
         <v>0</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.15">
@@ -7819,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.15">
@@ -7836,10 +7872,10 @@
         <v>0</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.15">
@@ -7853,10 +7889,10 @@
         <v>0</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.15">
@@ -7870,10 +7906,10 @@
         <v>0</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.15">
@@ -7887,10 +7923,10 @@
         <v>0</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.15">
@@ -7904,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.15">
@@ -7921,10 +7957,10 @@
         <v>0</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.15">
@@ -7938,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.15">
@@ -7955,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.15">
@@ -7972,10 +8008,10 @@
         <v>0</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.15">
@@ -7989,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.15">
@@ -8006,10 +8042,10 @@
         <v>0</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.15">
@@ -8023,10 +8059,10 @@
         <v>0</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.15">
@@ -8040,10 +8076,10 @@
         <v>0</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.15">
@@ -8057,10 +8093,10 @@
         <v>0</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.15">
@@ -8074,10 +8110,10 @@
         <v>0</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.15">
@@ -8091,10 +8127,10 @@
         <v>0</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.15">
@@ -8108,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.15">
@@ -8125,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.15">
@@ -8142,10 +8178,10 @@
         <v>0</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.15">
@@ -8159,10 +8195,10 @@
         <v>0</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.15">
@@ -8176,10 +8212,10 @@
         <v>0</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.15">
@@ -8193,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.15">
@@ -8210,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.15">
@@ -8227,10 +8263,10 @@
         <v>0</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.15">
@@ -8244,10 +8280,10 @@
         <v>0</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.15">
@@ -8261,10 +8297,10 @@
         <v>0</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.15">
@@ -8278,10 +8314,10 @@
         <v>0</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.15">
@@ -8295,10 +8331,10 @@
         <v>0</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.15">
@@ -8312,10 +8348,10 @@
         <v>0</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.15">
@@ -8329,10 +8365,10 @@
         <v>0</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.15">
@@ -8346,10 +8382,10 @@
         <v>0</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.15">
@@ -8363,10 +8399,10 @@
         <v>0</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.15">
@@ -8380,10 +8416,10 @@
         <v>0</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.15">
@@ -8397,10 +8433,10 @@
         <v>0</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.15">
@@ -8414,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.15">
@@ -8431,10 +8467,10 @@
         <v>0</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.15">
@@ -8448,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.15">
@@ -8465,10 +8501,10 @@
         <v>0</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.15">
@@ -8482,10 +8518,10 @@
         <v>0</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.15">
@@ -8499,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.15">
@@ -8516,10 +8552,10 @@
         <v>0</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.15">
@@ -8533,10 +8569,10 @@
         <v>0</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.15">
@@ -8550,10 +8586,10 @@
         <v>0</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.15">
@@ -8567,10 +8603,10 @@
         <v>0</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.15">
@@ -8584,10 +8620,10 @@
         <v>0</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.15">
@@ -8601,10 +8637,10 @@
         <v>0</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.15">
@@ -8618,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.15">
@@ -8635,10 +8671,10 @@
         <v>0</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.15">
@@ -8652,10 +8688,10 @@
         <v>0</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.15">
@@ -8669,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.15">
@@ -8686,10 +8722,10 @@
         <v>0</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.15">
@@ -8703,10 +8739,10 @@
         <v>0</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.15">
@@ -8720,10 +8756,10 @@
         <v>0</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.15">
@@ -8737,10 +8773,10 @@
         <v>0</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.15">
@@ -8754,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.15">
@@ -8771,10 +8807,10 @@
         <v>0</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.15">
@@ -8788,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.15">
@@ -8805,10 +8841,10 @@
         <v>0</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.15">
@@ -8822,10 +8858,10 @@
         <v>0</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.15">
@@ -8839,10 +8875,10 @@
         <v>0</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.15">
@@ -8856,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.15">
@@ -8873,10 +8909,10 @@
         <v>0</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.15">
@@ -8890,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.15">
@@ -8907,10 +8943,10 @@
         <v>0</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.15">
@@ -8924,10 +8960,10 @@
         <v>0</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.15">
@@ -8941,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.15">
@@ -8958,10 +8994,10 @@
         <v>0</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.15">
@@ -8975,10 +9011,10 @@
         <v>0</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD258453-968A-46A8-B218-CE31F8692284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C883DEB-3E82-42D9-A9ED-D71BF949B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="38">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,9 +83,6 @@
     <t>42761010,42663010</t>
   </si>
   <si>
-    <t>42652007</t>
-  </si>
-  <si>
     <t>drop_exp_num</t>
   </si>
   <si>
@@ -129,28 +126,10 @@
     <t>46700001:5</t>
   </si>
   <si>
-    <t>42761001</t>
-  </si>
-  <si>
-    <t>42663002</t>
-  </si>
-  <si>
-    <t>42761003</t>
-  </si>
-  <si>
     <t>46700001:6</t>
   </si>
   <si>
-    <t>42663004</t>
-  </si>
-  <si>
     <t>46700001:7</t>
-  </si>
-  <si>
-    <t>42655004</t>
-  </si>
-  <si>
-    <t>42761005</t>
   </si>
   <si>
     <t>46700001:12</t>
@@ -162,25 +141,13 @@
     <t>46200001:60</t>
   </si>
   <si>
-    <t>42663006</t>
-  </si>
-  <si>
     <t>46700001:13</t>
-  </si>
-  <si>
-    <t>42657006</t>
   </si>
   <si>
     <t>46700001:10</t>
   </si>
   <si>
     <t>46200001:80</t>
-  </si>
-  <si>
-    <t>42664006</t>
-  </si>
-  <si>
-    <t>42761007</t>
   </si>
   <si>
     <t>46700001:17</t>
@@ -193,9 +160,6 @@
   </si>
   <si>
     <t>46200001:120</t>
-  </si>
-  <si>
-    <t>42668007</t>
   </si>
   <si>
     <t>46700001:18</t>
@@ -564,19 +528,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -593,10 +557,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -613,10 +577,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -626,14 +590,14 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
+      <c r="D5" s="2">
+        <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -647,10 +611,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -660,14 +624,14 @@
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
+      <c r="D7" s="2">
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -681,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -694,14 +658,14 @@
       <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
+      <c r="D9" s="2">
+        <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -715,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -728,14 +692,14 @@
       <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
+      <c r="D11" s="2">
+        <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -749,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -762,14 +726,14 @@
       <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -779,14 +743,14 @@
       <c r="B14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
+      <c r="D14" s="2">
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -800,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -817,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -834,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
@@ -847,14 +811,14 @@
       <c r="B18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>37</v>
+      <c r="D18" s="2">
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -868,10 +832,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -881,14 +845,14 @@
       <c r="B20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>39</v>
+      <c r="D20" s="2">
+        <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -902,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -919,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -932,14 +896,14 @@
       <c r="B23" s="1">
         <v>6</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>42</v>
+      <c r="D23" s="2">
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -953,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -966,14 +930,14 @@
       <c r="B25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>43</v>
+      <c r="D25" s="2">
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -987,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -1004,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -1017,14 +981,14 @@
       <c r="B28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>12</v>
+      <c r="D28" s="2">
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
@@ -1038,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1055,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1068,14 +1032,14 @@
       <c r="B31" s="1">
         <v>7</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
+      <c r="D31" s="2">
+        <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1089,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1106,10 +1070,10 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1123,10 +1087,10 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1140,10 +1104,10 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1157,10 +1121,10 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1174,10 +1138,10 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1191,10 +1155,10 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1208,10 +1172,10 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1225,10 +1189,10 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
@@ -1242,10 +1206,10 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1259,10 +1223,10 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1276,10 +1240,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1293,10 +1257,10 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1310,10 +1274,10 @@
         <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1327,10 +1291,10 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1344,10 +1308,10 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1361,10 +1325,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1378,10 +1342,10 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -1395,10 +1359,10 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -1412,10 +1376,10 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
@@ -1429,10 +1393,10 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -1446,10 +1410,10 @@
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -1463,10 +1427,10 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -1480,10 +1444,10 @@
         <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -1497,10 +1461,10 @@
         <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -1514,10 +1478,10 @@
         <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -1531,10 +1495,10 @@
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -1548,10 +1512,10 @@
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -1565,10 +1529,10 @@
         <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -1582,10 +1546,10 @@
         <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
@@ -1599,10 +1563,10 @@
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
@@ -1616,10 +1580,10 @@
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -1633,10 +1597,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -1650,10 +1614,10 @@
         <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -1667,10 +1631,10 @@
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -1684,10 +1648,10 @@
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -1701,10 +1665,10 @@
         <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -1718,10 +1682,10 @@
         <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -1735,10 +1699,10 @@
         <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -1752,10 +1716,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -1769,10 +1733,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -1786,10 +1750,10 @@
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -1803,10 +1767,10 @@
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -1820,10 +1784,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -1837,10 +1801,10 @@
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -1854,10 +1818,10 @@
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -1871,10 +1835,10 @@
         <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -1888,10 +1852,10 @@
         <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -1905,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -1922,10 +1886,10 @@
         <v>11</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -1939,10 +1903,10 @@
         <v>11</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -1956,10 +1920,10 @@
         <v>11</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
@@ -1973,10 +1937,10 @@
         <v>11</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -1990,10 +1954,10 @@
         <v>11</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -2007,10 +1971,10 @@
         <v>11</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -2024,10 +1988,10 @@
         <v>11</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2041,10 +2005,10 @@
         <v>11</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2058,10 +2022,10 @@
         <v>11</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2075,10 +2039,10 @@
         <v>11</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2092,10 +2056,10 @@
         <v>11</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2109,10 +2073,10 @@
         <v>11</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2126,10 +2090,10 @@
         <v>11</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2143,10 +2107,10 @@
         <v>11</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2160,10 +2124,10 @@
         <v>11</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2177,10 +2141,10 @@
         <v>11</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
@@ -2194,10 +2158,10 @@
         <v>11</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2211,10 +2175,10 @@
         <v>11</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
@@ -2228,10 +2192,10 @@
         <v>11</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
@@ -2245,10 +2209,10 @@
         <v>11</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
@@ -2262,10 +2226,10 @@
         <v>11</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
@@ -2279,10 +2243,10 @@
         <v>11</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
@@ -2296,10 +2260,10 @@
         <v>11</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
@@ -2313,10 +2277,10 @@
         <v>11</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
@@ -2330,10 +2294,10 @@
         <v>11</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
@@ -2347,10 +2311,10 @@
         <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
@@ -2364,10 +2328,10 @@
         <v>11</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
@@ -2381,10 +2345,10 @@
         <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
@@ -2398,10 +2362,10 @@
         <v>11</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
@@ -2415,10 +2379,10 @@
         <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
@@ -2432,10 +2396,10 @@
         <v>11</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
@@ -2449,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
@@ -2466,10 +2430,10 @@
         <v>11</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
@@ -2483,10 +2447,10 @@
         <v>11</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
@@ -2500,10 +2464,10 @@
         <v>11</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
@@ -2517,10 +2481,10 @@
         <v>11</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
@@ -2534,10 +2498,10 @@
         <v>11</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
@@ -2551,10 +2515,10 @@
         <v>11</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
@@ -2568,10 +2532,10 @@
         <v>11</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -2585,10 +2549,10 @@
         <v>11</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
@@ -2602,10 +2566,10 @@
         <v>11</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.15">
@@ -2619,10 +2583,10 @@
         <v>11</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.15">
@@ -2636,10 +2600,10 @@
         <v>11</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.15">
@@ -2653,10 +2617,10 @@
         <v>11</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.15">
@@ -2670,10 +2634,10 @@
         <v>11</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.15">
@@ -2687,10 +2651,10 @@
         <v>11</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.15">
@@ -2704,10 +2668,10 @@
         <v>11</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.15">
@@ -2721,10 +2685,10 @@
         <v>11</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.15">
@@ -2738,10 +2702,10 @@
         <v>11</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.15">
@@ -2755,10 +2719,10 @@
         <v>11</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -2772,10 +2736,10 @@
         <v>11</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -2789,10 +2753,10 @@
         <v>11</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
@@ -2806,10 +2770,10 @@
         <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
@@ -2823,10 +2787,10 @@
         <v>11</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
@@ -2840,10 +2804,10 @@
         <v>11</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
@@ -2857,10 +2821,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
@@ -2874,10 +2838,10 @@
         <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -2891,10 +2855,10 @@
         <v>11</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
@@ -2908,10 +2872,10 @@
         <v>11</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">
@@ -2925,10 +2889,10 @@
         <v>11</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
@@ -2942,10 +2906,10 @@
         <v>11</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -2959,10 +2923,10 @@
         <v>11</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -2976,10 +2940,10 @@
         <v>11</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -2993,10 +2957,10 @@
         <v>11</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
@@ -3010,10 +2974,10 @@
         <v>11</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
@@ -3027,10 +2991,10 @@
         <v>11</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
@@ -3044,10 +3008,10 @@
         <v>11</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
@@ -3061,10 +3025,10 @@
         <v>11</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
@@ -3078,10 +3042,10 @@
         <v>11</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
@@ -3095,10 +3059,10 @@
         <v>11</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
@@ -3112,10 +3076,10 @@
         <v>11</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.15">
@@ -3129,10 +3093,10 @@
         <v>11</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
@@ -3146,10 +3110,10 @@
         <v>11</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
@@ -3163,10 +3127,10 @@
         <v>11</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
@@ -3180,10 +3144,10 @@
         <v>11</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
@@ -3197,10 +3161,10 @@
         <v>11</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
@@ -3214,10 +3178,10 @@
         <v>11</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
@@ -3231,10 +3195,10 @@
         <v>11</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
@@ -3248,10 +3212,10 @@
         <v>11</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
@@ -3265,10 +3229,10 @@
         <v>11</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
@@ -3282,10 +3246,10 @@
         <v>11</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
@@ -3299,10 +3263,10 @@
         <v>11</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
@@ -3316,10 +3280,10 @@
         <v>11</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
@@ -3333,10 +3297,10 @@
         <v>11</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
@@ -3350,10 +3314,10 @@
         <v>11</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
@@ -3367,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -3384,10 +3348,10 @@
         <v>11</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -3401,10 +3365,10 @@
         <v>11</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
@@ -3418,10 +3382,10 @@
         <v>11</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
@@ -3435,10 +3399,10 @@
         <v>11</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
@@ -3452,10 +3416,10 @@
         <v>11</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
@@ -3469,10 +3433,10 @@
         <v>11</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
@@ -3486,10 +3450,10 @@
         <v>11</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
@@ -3503,10 +3467,10 @@
         <v>11</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
@@ -3520,10 +3484,10 @@
         <v>11</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
@@ -3537,10 +3501,10 @@
         <v>11</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
@@ -3554,10 +3518,10 @@
         <v>11</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
@@ -3571,10 +3535,10 @@
         <v>11</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
@@ -3588,10 +3552,10 @@
         <v>11</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
@@ -3605,10 +3569,10 @@
         <v>11</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
@@ -3622,10 +3586,10 @@
         <v>11</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
@@ -3639,10 +3603,10 @@
         <v>11</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
@@ -3656,10 +3620,10 @@
         <v>11</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
@@ -3673,10 +3637,10 @@
         <v>11</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
@@ -3690,10 +3654,10 @@
         <v>11</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
@@ -3707,10 +3671,10 @@
         <v>11</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
@@ -3724,10 +3688,10 @@
         <v>11</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
@@ -3741,10 +3705,10 @@
         <v>11</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
@@ -3758,10 +3722,10 @@
         <v>11</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
@@ -3775,10 +3739,10 @@
         <v>11</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
@@ -3792,10 +3756,10 @@
         <v>11</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
@@ -3809,10 +3773,10 @@
         <v>11</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
@@ -3826,10 +3790,10 @@
         <v>11</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
@@ -3843,10 +3807,10 @@
         <v>11</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
@@ -3860,10 +3824,10 @@
         <v>11</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
@@ -3877,10 +3841,10 @@
         <v>11</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
@@ -3894,10 +3858,10 @@
         <v>11</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
@@ -3911,10 +3875,10 @@
         <v>11</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
@@ -3928,10 +3892,10 @@
         <v>11</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
@@ -3945,10 +3909,10 @@
         <v>11</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
@@ -3962,10 +3926,10 @@
         <v>11</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
@@ -3979,10 +3943,10 @@
         <v>11</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
@@ -3996,10 +3960,10 @@
         <v>11</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
@@ -4013,10 +3977,10 @@
         <v>11</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
@@ -4030,10 +3994,10 @@
         <v>11</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
@@ -4047,10 +4011,10 @@
         <v>11</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
@@ -4064,10 +4028,10 @@
         <v>11</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
@@ -4081,10 +4045,10 @@
         <v>11</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
@@ -4098,10 +4062,10 @@
         <v>11</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -4115,10 +4079,10 @@
         <v>11</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
@@ -4132,10 +4096,10 @@
         <v>11</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
@@ -4149,10 +4113,10 @@
         <v>11</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
@@ -4166,10 +4130,10 @@
         <v>11</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
@@ -4183,10 +4147,10 @@
         <v>11</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
@@ -4200,10 +4164,10 @@
         <v>11</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
@@ -4217,10 +4181,10 @@
         <v>11</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
@@ -4234,10 +4198,10 @@
         <v>11</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
@@ -4251,10 +4215,10 @@
         <v>11</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
@@ -4268,10 +4232,10 @@
         <v>11</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
@@ -4285,10 +4249,10 @@
         <v>11</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
@@ -4302,10 +4266,10 @@
         <v>11</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
@@ -4319,10 +4283,10 @@
         <v>11</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
@@ -4336,10 +4300,10 @@
         <v>11</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
@@ -4353,10 +4317,10 @@
         <v>11</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
@@ -4370,10 +4334,10 @@
         <v>11</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
@@ -4387,10 +4351,10 @@
         <v>11</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
@@ -4404,10 +4368,10 @@
         <v>11</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
@@ -4421,10 +4385,10 @@
         <v>11</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
@@ -4438,10 +4402,10 @@
         <v>11</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
@@ -4455,10 +4419,10 @@
         <v>11</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
@@ -4472,10 +4436,10 @@
         <v>11</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
@@ -4489,10 +4453,10 @@
         <v>11</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
@@ -4506,10 +4470,10 @@
         <v>11</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
@@ -4523,10 +4487,10 @@
         <v>11</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
@@ -4540,10 +4504,10 @@
         <v>11</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
@@ -4557,10 +4521,10 @@
         <v>11</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
@@ -4574,10 +4538,10 @@
         <v>11</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
@@ -4591,10 +4555,10 @@
         <v>11</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
@@ -4608,10 +4572,10 @@
         <v>11</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
@@ -4625,10 +4589,10 @@
         <v>11</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
@@ -4642,10 +4606,10 @@
         <v>11</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
@@ -4659,10 +4623,10 @@
         <v>11</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
@@ -4676,10 +4640,10 @@
         <v>11</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
@@ -4693,10 +4657,10 @@
         <v>11</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
@@ -4710,10 +4674,10 @@
         <v>11</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
@@ -4727,10 +4691,10 @@
         <v>11</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
@@ -4744,10 +4708,10 @@
         <v>11</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
@@ -4761,10 +4725,10 @@
         <v>11</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
@@ -4778,10 +4742,10 @@
         <v>11</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
@@ -4795,10 +4759,10 @@
         <v>11</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.15">
@@ -4812,10 +4776,10 @@
         <v>11</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.15">
@@ -4829,10 +4793,10 @@
         <v>11</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.15">
@@ -4846,10 +4810,10 @@
         <v>11</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.15">
@@ -4863,10 +4827,10 @@
         <v>11</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.15">
@@ -4880,10 +4844,10 @@
         <v>11</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.15">
@@ -4897,10 +4861,10 @@
         <v>11</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.15">
@@ -4914,10 +4878,10 @@
         <v>11</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.15">
@@ -4931,10 +4895,10 @@
         <v>11</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.15">
@@ -4948,10 +4912,10 @@
         <v>11</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.15">
@@ -4965,10 +4929,10 @@
         <v>11</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.15">
@@ -4982,10 +4946,10 @@
         <v>11</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.15">
@@ -4999,10 +4963,10 @@
         <v>11</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.15">
@@ -5016,10 +4980,10 @@
         <v>11</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.15">
@@ -5033,10 +4997,10 @@
         <v>11</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.15">
@@ -5050,10 +5014,10 @@
         <v>11</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.15">
@@ -5067,10 +5031,10 @@
         <v>11</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.15">
@@ -5084,10 +5048,10 @@
         <v>11</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.15">
@@ -5101,10 +5065,10 @@
         <v>11</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.15">
@@ -5118,10 +5082,10 @@
         <v>11</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.15">
@@ -5135,10 +5099,10 @@
         <v>11</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.15">
@@ -5152,10 +5116,10 @@
         <v>11</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.15">
@@ -5169,10 +5133,10 @@
         <v>11</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.15">
@@ -5186,10 +5150,10 @@
         <v>11</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.15">
@@ -5203,10 +5167,10 @@
         <v>11</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.15">
@@ -5220,10 +5184,10 @@
         <v>11</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.15">
@@ -5237,10 +5201,10 @@
         <v>11</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.15">
@@ -5254,10 +5218,10 @@
         <v>11</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.15">
@@ -5271,10 +5235,10 @@
         <v>11</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.15">
@@ -5288,10 +5252,10 @@
         <v>11</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.15">
@@ -5305,10 +5269,10 @@
         <v>11</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.15">
@@ -5322,10 +5286,10 @@
         <v>11</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.15">
@@ -5339,10 +5303,10 @@
         <v>11</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.15">
@@ -5356,10 +5320,10 @@
         <v>11</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.15">
@@ -5373,10 +5337,10 @@
         <v>11</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.15">
@@ -5390,10 +5354,10 @@
         <v>11</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.15">
@@ -5407,10 +5371,10 @@
         <v>11</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.15">
@@ -5424,10 +5388,10 @@
         <v>11</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.15">
@@ -5441,10 +5405,10 @@
         <v>11</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.15">
@@ -5458,10 +5422,10 @@
         <v>11</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.15">
@@ -5475,10 +5439,10 @@
         <v>11</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.15">
@@ -5492,10 +5456,10 @@
         <v>11</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.15">
@@ -5509,10 +5473,10 @@
         <v>11</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.15">
@@ -5526,10 +5490,10 @@
         <v>11</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.15">
@@ -5543,10 +5507,10 @@
         <v>11</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.15">
@@ -5560,10 +5524,10 @@
         <v>11</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.15">
@@ -5577,10 +5541,10 @@
         <v>11</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.15">
@@ -5594,10 +5558,10 @@
         <v>11</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.15">
@@ -5611,10 +5575,10 @@
         <v>11</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.15">
@@ -5628,10 +5592,10 @@
         <v>11</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.15">
@@ -5645,10 +5609,10 @@
         <v>11</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.15">
@@ -5662,10 +5626,10 @@
         <v>11</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.15">
@@ -5679,10 +5643,10 @@
         <v>11</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.15">
@@ -5696,10 +5660,10 @@
         <v>11</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.15">
@@ -5713,10 +5677,10 @@
         <v>11</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.15">
@@ -5730,10 +5694,10 @@
         <v>11</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.15">
@@ -5747,10 +5711,10 @@
         <v>11</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.15">
@@ -5764,10 +5728,10 @@
         <v>11</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.15">
@@ -5781,10 +5745,10 @@
         <v>11</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.15">
@@ -5798,10 +5762,10 @@
         <v>11</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.15">
@@ -5815,10 +5779,10 @@
         <v>11</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.15">
@@ -5832,10 +5796,10 @@
         <v>11</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.15">
@@ -5849,10 +5813,10 @@
         <v>11</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.15">
@@ -5866,10 +5830,10 @@
         <v>11</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.15">
@@ -5883,10 +5847,10 @@
         <v>11</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.15">
@@ -5900,10 +5864,10 @@
         <v>11</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.15">
@@ -5917,10 +5881,10 @@
         <v>11</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.15">
@@ -5934,10 +5898,10 @@
         <v>11</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.15">
@@ -5951,10 +5915,10 @@
         <v>11</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.15">
@@ -5968,10 +5932,10 @@
         <v>11</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.15">
@@ -5985,10 +5949,10 @@
         <v>11</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.15">
@@ -6002,10 +5966,10 @@
         <v>11</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.15">
@@ -6019,10 +5983,10 @@
         <v>11</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.15">
@@ -6036,10 +6000,10 @@
         <v>11</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.15">
@@ -6053,10 +6017,10 @@
         <v>11</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.15">
@@ -6070,10 +6034,10 @@
         <v>11</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.15">
@@ -6087,10 +6051,10 @@
         <v>11</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.15">
@@ -6104,10 +6068,10 @@
         <v>11</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.15">
@@ -6121,10 +6085,10 @@
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.15">
@@ -6138,10 +6102,10 @@
         <v>11</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.15">
@@ -6155,10 +6119,10 @@
         <v>11</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.15">
@@ -6172,10 +6136,10 @@
         <v>11</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.15">
@@ -6189,10 +6153,10 @@
         <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.15">
@@ -6206,10 +6170,10 @@
         <v>11</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.15">
@@ -6223,10 +6187,10 @@
         <v>11</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.15">
@@ -6240,10 +6204,10 @@
         <v>11</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.15">
@@ -6257,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.15">
@@ -6274,10 +6238,10 @@
         <v>11</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.15">
@@ -6291,10 +6255,10 @@
         <v>11</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F338" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.15">
@@ -6308,10 +6272,10 @@
         <v>0</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.15">
@@ -6325,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.15">
@@ -6342,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.15">
@@ -6359,10 +6323,10 @@
         <v>0</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.15">
@@ -6376,10 +6340,10 @@
         <v>0</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.15">
@@ -6393,10 +6357,10 @@
         <v>0</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.15">
@@ -6410,10 +6374,10 @@
         <v>0</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.15">
@@ -6427,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.15">
@@ -6444,10 +6408,10 @@
         <v>0</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.15">
@@ -6461,10 +6425,10 @@
         <v>0</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.15">
@@ -6478,10 +6442,10 @@
         <v>0</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.15">
@@ -6495,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.15">
@@ -6512,10 +6476,10 @@
         <v>0</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.15">
@@ -6529,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.15">
@@ -6546,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.15">
@@ -6563,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.15">
@@ -6580,10 +6544,10 @@
         <v>0</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.15">
@@ -6597,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.15">
@@ -6614,10 +6578,10 @@
         <v>0</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.15">
@@ -6631,10 +6595,10 @@
         <v>0</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.15">
@@ -6648,10 +6612,10 @@
         <v>0</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.15">
@@ -6665,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.15">
@@ -6682,10 +6646,10 @@
         <v>0</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.15">
@@ -6699,10 +6663,10 @@
         <v>0</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.15">
@@ -6716,10 +6680,10 @@
         <v>0</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.15">
@@ -6733,10 +6697,10 @@
         <v>0</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.15">
@@ -6750,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.15">
@@ -6767,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.15">
@@ -6784,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.15">
@@ -6801,10 +6765,10 @@
         <v>0</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.15">
@@ -6818,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.15">
@@ -6835,10 +6799,10 @@
         <v>0</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.15">
@@ -6852,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.15">
@@ -6869,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.15">
@@ -6886,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.15">
@@ -6903,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.15">
@@ -6920,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.15">
@@ -6937,10 +6901,10 @@
         <v>0</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.15">
@@ -6954,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.15">
@@ -6971,10 +6935,10 @@
         <v>0</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.15">
@@ -6988,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.15">
@@ -7005,10 +6969,10 @@
         <v>0</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.15">
@@ -7022,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.15">
@@ -7039,10 +7003,10 @@
         <v>0</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.15">
@@ -7056,10 +7020,10 @@
         <v>0</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.15">
@@ -7073,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.15">
@@ -7090,10 +7054,10 @@
         <v>0</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.15">
@@ -7107,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.15">
@@ -7124,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.15">
@@ -7141,10 +7105,10 @@
         <v>0</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.15">
@@ -7158,10 +7122,10 @@
         <v>0</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.15">
@@ -7175,10 +7139,10 @@
         <v>0</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.15">
@@ -7192,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.15">
@@ -7209,10 +7173,10 @@
         <v>0</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.15">
@@ -7226,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.15">
@@ -7243,10 +7207,10 @@
         <v>0</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.15">
@@ -7260,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.15">
@@ -7277,10 +7241,10 @@
         <v>0</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.15">
@@ -7294,10 +7258,10 @@
         <v>0</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.15">
@@ -7311,10 +7275,10 @@
         <v>0</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.15">
@@ -7328,10 +7292,10 @@
         <v>0</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.15">
@@ -7345,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.15">
@@ -7362,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.15">
@@ -7379,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.15">
@@ -7396,10 +7360,10 @@
         <v>0</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.15">
@@ -7413,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.15">
@@ -7430,10 +7394,10 @@
         <v>0</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.15">
@@ -7447,10 +7411,10 @@
         <v>0</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.15">
@@ -7464,10 +7428,10 @@
         <v>0</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.15">
@@ -7481,10 +7445,10 @@
         <v>0</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.15">
@@ -7498,10 +7462,10 @@
         <v>0</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.15">
@@ -7515,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.15">
@@ -7532,10 +7496,10 @@
         <v>0</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.15">
@@ -7549,10 +7513,10 @@
         <v>0</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.15">
@@ -7566,10 +7530,10 @@
         <v>0</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.15">
@@ -7583,10 +7547,10 @@
         <v>0</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.15">
@@ -7600,10 +7564,10 @@
         <v>0</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.15">
@@ -7617,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.15">
@@ -7634,10 +7598,10 @@
         <v>0</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.15">
@@ -7651,10 +7615,10 @@
         <v>0</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.15">
@@ -7668,10 +7632,10 @@
         <v>0</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.15">
@@ -7685,10 +7649,10 @@
         <v>0</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.15">
@@ -7702,10 +7666,10 @@
         <v>0</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.15">
@@ -7719,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.15">
@@ -7736,10 +7700,10 @@
         <v>0</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.15">
@@ -7753,10 +7717,10 @@
         <v>0</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.15">
@@ -7770,10 +7734,10 @@
         <v>0</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.15">
@@ -7787,10 +7751,10 @@
         <v>0</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.15">
@@ -7804,10 +7768,10 @@
         <v>0</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.15">
@@ -7821,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.15">
@@ -7838,10 +7802,10 @@
         <v>0</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.15">
@@ -7855,10 +7819,10 @@
         <v>0</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.15">
@@ -7872,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.15">
@@ -7889,10 +7853,10 @@
         <v>0</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.15">
@@ -7906,10 +7870,10 @@
         <v>0</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.15">
@@ -7923,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.15">
@@ -7940,10 +7904,10 @@
         <v>0</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.15">
@@ -7957,10 +7921,10 @@
         <v>0</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.15">
@@ -7974,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.15">
@@ -7991,10 +7955,10 @@
         <v>0</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.15">
@@ -8008,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.15">
@@ -8025,10 +7989,10 @@
         <v>0</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.15">
@@ -8042,10 +8006,10 @@
         <v>0</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.15">
@@ -8059,10 +8023,10 @@
         <v>0</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.15">
@@ -8076,10 +8040,10 @@
         <v>0</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.15">
@@ -8093,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.15">
@@ -8110,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.15">
@@ -8127,10 +8091,10 @@
         <v>0</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.15">
@@ -8144,10 +8108,10 @@
         <v>0</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.15">
@@ -8161,10 +8125,10 @@
         <v>0</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.15">
@@ -8178,10 +8142,10 @@
         <v>0</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.15">
@@ -8195,10 +8159,10 @@
         <v>0</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.15">
@@ -8212,10 +8176,10 @@
         <v>0</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.15">
@@ -8229,10 +8193,10 @@
         <v>0</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.15">
@@ -8246,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.15">
@@ -8263,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.15">
@@ -8280,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.15">
@@ -8297,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.15">
@@ -8314,10 +8278,10 @@
         <v>0</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.15">
@@ -8331,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.15">
@@ -8348,10 +8312,10 @@
         <v>0</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.15">
@@ -8365,10 +8329,10 @@
         <v>0</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.15">
@@ -8382,10 +8346,10 @@
         <v>0</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.15">
@@ -8399,10 +8363,10 @@
         <v>0</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.15">
@@ -8416,10 +8380,10 @@
         <v>0</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.15">
@@ -8433,10 +8397,10 @@
         <v>0</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.15">
@@ -8450,10 +8414,10 @@
         <v>0</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.15">
@@ -8467,10 +8431,10 @@
         <v>0</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.15">
@@ -8484,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.15">
@@ -8501,10 +8465,10 @@
         <v>0</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.15">
@@ -8518,10 +8482,10 @@
         <v>0</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.15">
@@ -8535,10 +8499,10 @@
         <v>0</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.15">
@@ -8552,10 +8516,10 @@
         <v>0</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.15">
@@ -8569,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.15">
@@ -8586,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.15">
@@ -8603,10 +8567,10 @@
         <v>0</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.15">
@@ -8620,10 +8584,10 @@
         <v>0</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.15">
@@ -8637,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.15">
@@ -8654,10 +8618,10 @@
         <v>0</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.15">
@@ -8671,10 +8635,10 @@
         <v>0</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.15">
@@ -8688,10 +8652,10 @@
         <v>0</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.15">
@@ -8705,10 +8669,10 @@
         <v>0</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.15">
@@ -8722,10 +8686,10 @@
         <v>0</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.15">
@@ -8739,10 +8703,10 @@
         <v>0</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.15">
@@ -8756,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.15">
@@ -8773,10 +8737,10 @@
         <v>0</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.15">
@@ -8790,10 +8754,10 @@
         <v>0</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.15">
@@ -8807,10 +8771,10 @@
         <v>0</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.15">
@@ -8824,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.15">
@@ -8841,10 +8805,10 @@
         <v>0</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.15">
@@ -8858,10 +8822,10 @@
         <v>0</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.15">
@@ -8875,10 +8839,10 @@
         <v>0</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.15">
@@ -8892,10 +8856,10 @@
         <v>0</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.15">
@@ -8909,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.15">
@@ -8926,10 +8890,10 @@
         <v>0</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.15">
@@ -8943,10 +8907,10 @@
         <v>0</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.15">
@@ -8960,10 +8924,10 @@
         <v>0</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.15">
@@ -8977,10 +8941,10 @@
         <v>0</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.15">
@@ -8994,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.15">
@@ -9011,10 +8975,10 @@
         <v>0</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C883DEB-3E82-42D9-A9ED-D71BF949B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A5526B-7FCE-4A3D-9D40-2DFC3E3F8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="41">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,18 @@
   </si>
   <si>
     <t>46700001:18</t>
+  </si>
+  <si>
+    <t>add_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加通关值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -506,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F498"/>
+  <dimension ref="A1:G498"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -515,15 +527,16 @@
     <col min="4" max="4" width="39.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -542,8 +555,11 @@
       <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -562,8 +578,11 @@
       <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -582,8 +601,11 @@
       <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>10020</v>
       </c>
@@ -599,8 +621,11 @@
       <c r="F5" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10010</v>
       </c>
@@ -616,8 +641,11 @@
       <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>20020</v>
       </c>
@@ -633,8 +661,11 @@
       <c r="F7" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>20010</v>
       </c>
@@ -650,8 +681,11 @@
       <c r="F8" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>30020</v>
       </c>
@@ -667,8 +701,11 @@
       <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>30010</v>
       </c>
@@ -684,8 +721,11 @@
       <c r="F10" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>40020</v>
       </c>
@@ -701,8 +741,11 @@
       <c r="F11" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>40010</v>
       </c>
@@ -718,8 +761,11 @@
       <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>40002</v>
       </c>
@@ -735,8 +781,11 @@
       <c r="F13" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>50020</v>
       </c>
@@ -752,8 +801,11 @@
       <c r="F14" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>50010</v>
       </c>
@@ -769,8 +821,11 @@
       <c r="F15" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>50002</v>
       </c>
@@ -786,8 +841,11 @@
       <c r="F16" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>50003</v>
       </c>
@@ -803,8 +861,11 @@
       <c r="F17" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>60020</v>
       </c>
@@ -820,8 +881,11 @@
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>60010</v>
       </c>
@@ -837,8 +901,11 @@
       <c r="F19" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>60002</v>
       </c>
@@ -854,8 +921,11 @@
       <c r="F20" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>60003</v>
       </c>
@@ -871,8 +941,11 @@
       <c r="F21" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>60004</v>
       </c>
@@ -888,8 +961,11 @@
       <c r="F22" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>60005</v>
       </c>
@@ -905,8 +981,11 @@
       <c r="F23" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>60006</v>
       </c>
@@ -922,8 +1001,11 @@
       <c r="F24" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>70020</v>
       </c>
@@ -939,8 +1021,11 @@
       <c r="F25" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>70010</v>
       </c>
@@ -956,8 +1041,11 @@
       <c r="F26" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>70002</v>
       </c>
@@ -973,8 +1061,11 @@
       <c r="F27" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>70003</v>
       </c>
@@ -990,8 +1081,11 @@
       <c r="F28" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G28" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>70004</v>
       </c>
@@ -1007,8 +1101,11 @@
       <c r="F29" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G29" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>70005</v>
       </c>
@@ -1024,8 +1121,11 @@
       <c r="F30" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G30" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>70006</v>
       </c>
@@ -1041,8 +1141,11 @@
       <c r="F31" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G31" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>70007</v>
       </c>
@@ -1058,8 +1161,11 @@
       <c r="F32" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G32" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>80020</v>
       </c>
@@ -1075,8 +1181,11 @@
       <c r="F33" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>80010</v>
       </c>
@@ -1092,8 +1201,11 @@
       <c r="F34" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>90020</v>
       </c>
@@ -1109,8 +1221,11 @@
       <c r="F35" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>90010</v>
       </c>
@@ -1126,8 +1241,11 @@
       <c r="F36" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>100020</v>
       </c>
@@ -1143,8 +1261,11 @@
       <c r="F37" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>100010</v>
       </c>
@@ -1160,8 +1281,11 @@
       <c r="F38" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>110020</v>
       </c>
@@ -1177,8 +1301,11 @@
       <c r="F39" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>110010</v>
       </c>
@@ -1194,8 +1321,11 @@
       <c r="F40" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>120020</v>
       </c>
@@ -1211,8 +1341,11 @@
       <c r="F41" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>120010</v>
       </c>
@@ -1228,8 +1361,11 @@
       <c r="F42" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>130020</v>
       </c>
@@ -1245,8 +1381,11 @@
       <c r="F43" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>130010</v>
       </c>
@@ -1262,8 +1401,11 @@
       <c r="F44" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>140020</v>
       </c>
@@ -1279,8 +1421,11 @@
       <c r="F45" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>140010</v>
       </c>
@@ -1296,8 +1441,11 @@
       <c r="F46" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>150020</v>
       </c>
@@ -1313,8 +1461,11 @@
       <c r="F47" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>150010</v>
       </c>
@@ -1330,8 +1481,11 @@
       <c r="F48" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>160020</v>
       </c>
@@ -1347,8 +1501,11 @@
       <c r="F49" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>160010</v>
       </c>
@@ -1364,8 +1521,11 @@
       <c r="F50" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>170020</v>
       </c>
@@ -1381,8 +1541,11 @@
       <c r="F51" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>170010</v>
       </c>
@@ -1398,8 +1561,11 @@
       <c r="F52" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>180020</v>
       </c>
@@ -1415,8 +1581,11 @@
       <c r="F53" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>180010</v>
       </c>
@@ -1432,8 +1601,11 @@
       <c r="F54" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>190020</v>
       </c>
@@ -1449,8 +1621,11 @@
       <c r="F55" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>190010</v>
       </c>
@@ -1466,8 +1641,11 @@
       <c r="F56" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>200020</v>
       </c>
@@ -1483,8 +1661,11 @@
       <c r="F57" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>200010</v>
       </c>
@@ -1500,8 +1681,11 @@
       <c r="F58" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>210020</v>
       </c>
@@ -1517,8 +1701,11 @@
       <c r="F59" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>210010</v>
       </c>
@@ -1534,8 +1721,11 @@
       <c r="F60" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>220020</v>
       </c>
@@ -1551,8 +1741,11 @@
       <c r="F61" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>220010</v>
       </c>
@@ -1568,8 +1761,11 @@
       <c r="F62" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>230020</v>
       </c>
@@ -1585,8 +1781,11 @@
       <c r="F63" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>230010</v>
       </c>
@@ -1602,8 +1801,11 @@
       <c r="F64" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>240020</v>
       </c>
@@ -1619,8 +1821,11 @@
       <c r="F65" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>240010</v>
       </c>
@@ -1636,8 +1841,11 @@
       <c r="F66" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>250020</v>
       </c>
@@ -1653,8 +1861,11 @@
       <c r="F67" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>250010</v>
       </c>
@@ -1670,8 +1881,11 @@
       <c r="F68" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>260020</v>
       </c>
@@ -1687,8 +1901,11 @@
       <c r="F69" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>260010</v>
       </c>
@@ -1704,8 +1921,11 @@
       <c r="F70" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>270020</v>
       </c>
@@ -1721,8 +1941,11 @@
       <c r="F71" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>270010</v>
       </c>
@@ -1738,8 +1961,11 @@
       <c r="F72" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>280020</v>
       </c>
@@ -1755,8 +1981,11 @@
       <c r="F73" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>280010</v>
       </c>
@@ -1772,8 +2001,11 @@
       <c r="F74" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>290020</v>
       </c>
@@ -1789,8 +2021,11 @@
       <c r="F75" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>290010</v>
       </c>
@@ -1806,8 +2041,11 @@
       <c r="F76" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>300020</v>
       </c>
@@ -1823,8 +2061,11 @@
       <c r="F77" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>300010</v>
       </c>
@@ -1840,8 +2081,11 @@
       <c r="F78" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>310020</v>
       </c>
@@ -1857,8 +2101,11 @@
       <c r="F79" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>310010</v>
       </c>
@@ -1874,8 +2121,11 @@
       <c r="F80" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>320020</v>
       </c>
@@ -1891,8 +2141,11 @@
       <c r="F81" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>320010</v>
       </c>
@@ -1908,8 +2161,11 @@
       <c r="F82" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>330020</v>
       </c>
@@ -1925,8 +2181,11 @@
       <c r="F83" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>330010</v>
       </c>
@@ -1942,8 +2201,11 @@
       <c r="F84" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>340020</v>
       </c>
@@ -1959,8 +2221,11 @@
       <c r="F85" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>340010</v>
       </c>
@@ -1976,8 +2241,11 @@
       <c r="F86" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>350020</v>
       </c>
@@ -1993,8 +2261,11 @@
       <c r="F87" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>350010</v>
       </c>
@@ -2010,8 +2281,11 @@
       <c r="F88" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>360020</v>
       </c>
@@ -2027,8 +2301,11 @@
       <c r="F89" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>360010</v>
       </c>
@@ -2044,8 +2321,11 @@
       <c r="F90" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>370020</v>
       </c>
@@ -2061,8 +2341,11 @@
       <c r="F91" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>370010</v>
       </c>
@@ -2078,8 +2361,11 @@
       <c r="F92" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>380020</v>
       </c>
@@ -2095,8 +2381,11 @@
       <c r="F93" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>380010</v>
       </c>
@@ -2112,8 +2401,11 @@
       <c r="F94" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>390020</v>
       </c>
@@ -2129,8 +2421,11 @@
       <c r="F95" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>390010</v>
       </c>
@@ -2146,8 +2441,11 @@
       <c r="F96" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>400020</v>
       </c>
@@ -2163,8 +2461,11 @@
       <c r="F97" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>400010</v>
       </c>
@@ -2180,8 +2481,11 @@
       <c r="F98" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>410020</v>
       </c>
@@ -2197,8 +2501,11 @@
       <c r="F99" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>410010</v>
       </c>
@@ -2214,8 +2521,11 @@
       <c r="F100" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>420020</v>
       </c>
@@ -2231,8 +2541,11 @@
       <c r="F101" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>420010</v>
       </c>
@@ -2248,8 +2561,11 @@
       <c r="F102" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>430020</v>
       </c>
@@ -2265,8 +2581,11 @@
       <c r="F103" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>430010</v>
       </c>
@@ -2282,8 +2601,11 @@
       <c r="F104" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>440020</v>
       </c>
@@ -2299,8 +2621,11 @@
       <c r="F105" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>440010</v>
       </c>
@@ -2316,8 +2641,11 @@
       <c r="F106" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>450020</v>
       </c>
@@ -2333,8 +2661,11 @@
       <c r="F107" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>450010</v>
       </c>
@@ -2350,8 +2681,11 @@
       <c r="F108" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>460020</v>
       </c>
@@ -2367,8 +2701,11 @@
       <c r="F109" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>460010</v>
       </c>
@@ -2384,8 +2721,11 @@
       <c r="F110" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>470020</v>
       </c>
@@ -2401,8 +2741,11 @@
       <c r="F111" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>470010</v>
       </c>
@@ -2418,8 +2761,11 @@
       <c r="F112" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>480020</v>
       </c>
@@ -2435,8 +2781,11 @@
       <c r="F113" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>480010</v>
       </c>
@@ -2452,8 +2801,11 @@
       <c r="F114" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>490020</v>
       </c>
@@ -2469,8 +2821,11 @@
       <c r="F115" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>490010</v>
       </c>
@@ -2486,8 +2841,11 @@
       <c r="F116" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>500020</v>
       </c>
@@ -2503,8 +2861,11 @@
       <c r="F117" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>500010</v>
       </c>
@@ -2520,8 +2881,11 @@
       <c r="F118" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>510020</v>
       </c>
@@ -2537,8 +2901,11 @@
       <c r="F119" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>510010</v>
       </c>
@@ -2554,8 +2921,11 @@
       <c r="F120" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>520020</v>
       </c>
@@ -2571,8 +2941,11 @@
       <c r="F121" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>520010</v>
       </c>
@@ -2588,8 +2961,11 @@
       <c r="F122" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>530020</v>
       </c>
@@ -2605,8 +2981,11 @@
       <c r="F123" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>530010</v>
       </c>
@@ -2622,8 +3001,11 @@
       <c r="F124" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>540020</v>
       </c>
@@ -2639,8 +3021,11 @@
       <c r="F125" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>540010</v>
       </c>
@@ -2656,8 +3041,11 @@
       <c r="F126" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>550020</v>
       </c>
@@ -2673,8 +3061,11 @@
       <c r="F127" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>550010</v>
       </c>
@@ -2690,8 +3081,11 @@
       <c r="F128" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>560020</v>
       </c>
@@ -2707,8 +3101,11 @@
       <c r="F129" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>560010</v>
       </c>
@@ -2724,8 +3121,11 @@
       <c r="F130" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>570020</v>
       </c>
@@ -2741,8 +3141,11 @@
       <c r="F131" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>570010</v>
       </c>
@@ -2758,8 +3161,11 @@
       <c r="F132" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>580020</v>
       </c>
@@ -2775,8 +3181,11 @@
       <c r="F133" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>580010</v>
       </c>
@@ -2792,8 +3201,11 @@
       <c r="F134" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>590020</v>
       </c>
@@ -2809,8 +3221,11 @@
       <c r="F135" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>590010</v>
       </c>
@@ -2826,8 +3241,11 @@
       <c r="F136" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>600020</v>
       </c>
@@ -2843,8 +3261,11 @@
       <c r="F137" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>600010</v>
       </c>
@@ -2860,8 +3281,11 @@
       <c r="F138" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>610020</v>
       </c>
@@ -2877,8 +3301,11 @@
       <c r="F139" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>610010</v>
       </c>
@@ -2894,8 +3321,11 @@
       <c r="F140" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>620020</v>
       </c>
@@ -2911,8 +3341,11 @@
       <c r="F141" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>620010</v>
       </c>
@@ -2928,8 +3361,11 @@
       <c r="F142" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>630020</v>
       </c>
@@ -2945,8 +3381,11 @@
       <c r="F143" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>630010</v>
       </c>
@@ -2962,8 +3401,11 @@
       <c r="F144" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>640020</v>
       </c>
@@ -2979,8 +3421,11 @@
       <c r="F145" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>640010</v>
       </c>
@@ -2996,8 +3441,11 @@
       <c r="F146" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>650020</v>
       </c>
@@ -3013,8 +3461,11 @@
       <c r="F147" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>650010</v>
       </c>
@@ -3030,8 +3481,11 @@
       <c r="F148" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>660020</v>
       </c>
@@ -3047,8 +3501,11 @@
       <c r="F149" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>660010</v>
       </c>
@@ -3064,8 +3521,11 @@
       <c r="F150" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>670020</v>
       </c>
@@ -3081,8 +3541,11 @@
       <c r="F151" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>670010</v>
       </c>
@@ -3098,8 +3561,11 @@
       <c r="F152" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>680020</v>
       </c>
@@ -3115,8 +3581,11 @@
       <c r="F153" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>680010</v>
       </c>
@@ -3132,8 +3601,11 @@
       <c r="F154" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>690020</v>
       </c>
@@ -3149,8 +3621,11 @@
       <c r="F155" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>690010</v>
       </c>
@@ -3166,8 +3641,11 @@
       <c r="F156" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>700020</v>
       </c>
@@ -3183,8 +3661,11 @@
       <c r="F157" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>700010</v>
       </c>
@@ -3200,8 +3681,11 @@
       <c r="F158" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>710020</v>
       </c>
@@ -3217,8 +3701,11 @@
       <c r="F159" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>710010</v>
       </c>
@@ -3234,8 +3721,11 @@
       <c r="F160" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>720020</v>
       </c>
@@ -3251,8 +3741,11 @@
       <c r="F161" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>720010</v>
       </c>
@@ -3268,8 +3761,11 @@
       <c r="F162" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>730020</v>
       </c>
@@ -3285,8 +3781,11 @@
       <c r="F163" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>730010</v>
       </c>
@@ -3302,8 +3801,11 @@
       <c r="F164" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>740020</v>
       </c>
@@ -3319,8 +3821,11 @@
       <c r="F165" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>740010</v>
       </c>
@@ -3336,8 +3841,11 @@
       <c r="F166" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>750020</v>
       </c>
@@ -3353,8 +3861,11 @@
       <c r="F167" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>750010</v>
       </c>
@@ -3370,8 +3881,11 @@
       <c r="F168" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>760020</v>
       </c>
@@ -3387,8 +3901,11 @@
       <c r="F169" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>760010</v>
       </c>
@@ -3404,8 +3921,11 @@
       <c r="F170" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>770020</v>
       </c>
@@ -3421,8 +3941,11 @@
       <c r="F171" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>770010</v>
       </c>
@@ -3438,8 +3961,11 @@
       <c r="F172" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>780020</v>
       </c>
@@ -3455,8 +3981,11 @@
       <c r="F173" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>780010</v>
       </c>
@@ -3472,8 +4001,11 @@
       <c r="F174" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G174" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>790020</v>
       </c>
@@ -3489,8 +4021,11 @@
       <c r="F175" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G175" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>790010</v>
       </c>
@@ -3506,8 +4041,11 @@
       <c r="F176" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>800020</v>
       </c>
@@ -3523,8 +4061,11 @@
       <c r="F177" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>800010</v>
       </c>
@@ -3540,8 +4081,11 @@
       <c r="F178" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>810020</v>
       </c>
@@ -3557,8 +4101,11 @@
       <c r="F179" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>810010</v>
       </c>
@@ -3574,8 +4121,11 @@
       <c r="F180" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>820020</v>
       </c>
@@ -3591,8 +4141,11 @@
       <c r="F181" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>820010</v>
       </c>
@@ -3608,8 +4161,11 @@
       <c r="F182" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>830020</v>
       </c>
@@ -3625,8 +4181,11 @@
       <c r="F183" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>830010</v>
       </c>
@@ -3642,8 +4201,11 @@
       <c r="F184" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>840020</v>
       </c>
@@ -3659,8 +4221,11 @@
       <c r="F185" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>840010</v>
       </c>
@@ -3676,8 +4241,11 @@
       <c r="F186" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>850020</v>
       </c>
@@ -3693,8 +4261,11 @@
       <c r="F187" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>850010</v>
       </c>
@@ -3710,8 +4281,11 @@
       <c r="F188" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G188" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>860020</v>
       </c>
@@ -3727,8 +4301,11 @@
       <c r="F189" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G189" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>860010</v>
       </c>
@@ -3744,8 +4321,11 @@
       <c r="F190" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G190" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>870020</v>
       </c>
@@ -3761,8 +4341,11 @@
       <c r="F191" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G191" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>870010</v>
       </c>
@@ -3778,8 +4361,11 @@
       <c r="F192" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G192" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>880020</v>
       </c>
@@ -3795,8 +4381,11 @@
       <c r="F193" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G193" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>880010</v>
       </c>
@@ -3812,8 +4401,11 @@
       <c r="F194" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G194" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>890020</v>
       </c>
@@ -3829,8 +4421,11 @@
       <c r="F195" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G195" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>890010</v>
       </c>
@@ -3846,8 +4441,11 @@
       <c r="F196" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G196" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>900020</v>
       </c>
@@ -3863,8 +4461,11 @@
       <c r="F197" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G197" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>900010</v>
       </c>
@@ -3880,8 +4481,11 @@
       <c r="F198" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G198" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>910020</v>
       </c>
@@ -3897,8 +4501,11 @@
       <c r="F199" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G199" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>910010</v>
       </c>
@@ -3914,8 +4521,11 @@
       <c r="F200" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G200" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>920020</v>
       </c>
@@ -3931,8 +4541,11 @@
       <c r="F201" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>920010</v>
       </c>
@@ -3948,8 +4561,11 @@
       <c r="F202" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G202" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>930020</v>
       </c>
@@ -3965,8 +4581,11 @@
       <c r="F203" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G203" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>930010</v>
       </c>
@@ -3982,8 +4601,11 @@
       <c r="F204" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G204" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>940020</v>
       </c>
@@ -3999,8 +4621,11 @@
       <c r="F205" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G205" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>940010</v>
       </c>
@@ -4016,8 +4641,11 @@
       <c r="F206" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G206" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>950020</v>
       </c>
@@ -4033,8 +4661,11 @@
       <c r="F207" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G207" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>950010</v>
       </c>
@@ -4050,8 +4681,11 @@
       <c r="F208" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G208" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>960020</v>
       </c>
@@ -4067,8 +4701,11 @@
       <c r="F209" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G209" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>960010</v>
       </c>
@@ -4084,8 +4721,11 @@
       <c r="F210" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G210" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>970020</v>
       </c>
@@ -4101,8 +4741,11 @@
       <c r="F211" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G211" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>970010</v>
       </c>
@@ -4118,8 +4761,11 @@
       <c r="F212" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G212" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>980020</v>
       </c>
@@ -4135,8 +4781,11 @@
       <c r="F213" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G213" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>980010</v>
       </c>
@@ -4152,8 +4801,11 @@
       <c r="F214" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G214" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>990020</v>
       </c>
@@ -4169,8 +4821,11 @@
       <c r="F215" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G215" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>990010</v>
       </c>
@@ -4186,8 +4841,11 @@
       <c r="F216" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G216" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>1000020</v>
       </c>
@@ -4203,8 +4861,11 @@
       <c r="F217" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G217" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>1000010</v>
       </c>
@@ -4220,8 +4881,11 @@
       <c r="F218" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G218" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>1010020</v>
       </c>
@@ -4237,8 +4901,11 @@
       <c r="F219" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G219" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>1010010</v>
       </c>
@@ -4254,8 +4921,11 @@
       <c r="F220" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G220" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>1020020</v>
       </c>
@@ -4271,8 +4941,11 @@
       <c r="F221" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G221" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>1020010</v>
       </c>
@@ -4288,8 +4961,11 @@
       <c r="F222" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G222" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>1030020</v>
       </c>
@@ -4305,8 +4981,11 @@
       <c r="F223" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G223" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>1030010</v>
       </c>
@@ -4322,8 +5001,11 @@
       <c r="F224" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G224" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>1040020</v>
       </c>
@@ -4339,8 +5021,11 @@
       <c r="F225" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G225" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>1040010</v>
       </c>
@@ -4356,8 +5041,11 @@
       <c r="F226" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G226" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>1050020</v>
       </c>
@@ -4373,8 +5061,11 @@
       <c r="F227" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G227" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>1050010</v>
       </c>
@@ -4390,8 +5081,11 @@
       <c r="F228" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G228" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>1060020</v>
       </c>
@@ -4407,8 +5101,11 @@
       <c r="F229" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G229" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>1060010</v>
       </c>
@@ -4424,8 +5121,11 @@
       <c r="F230" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G230" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>1070020</v>
       </c>
@@ -4441,8 +5141,11 @@
       <c r="F231" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G231" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>1070010</v>
       </c>
@@ -4458,8 +5161,11 @@
       <c r="F232" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G232" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>1080020</v>
       </c>
@@ -4475,8 +5181,11 @@
       <c r="F233" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G233" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>1080010</v>
       </c>
@@ -4492,8 +5201,11 @@
       <c r="F234" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G234" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>1090020</v>
       </c>
@@ -4509,8 +5221,11 @@
       <c r="F235" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G235" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>1090010</v>
       </c>
@@ -4526,8 +5241,11 @@
       <c r="F236" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G236" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>1100020</v>
       </c>
@@ -4543,8 +5261,11 @@
       <c r="F237" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G237" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>1100010</v>
       </c>
@@ -4560,8 +5281,11 @@
       <c r="F238" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G238" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>1110020</v>
       </c>
@@ -4577,8 +5301,11 @@
       <c r="F239" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G239" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>1110010</v>
       </c>
@@ -4594,8 +5321,11 @@
       <c r="F240" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G240" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>1120020</v>
       </c>
@@ -4611,8 +5341,11 @@
       <c r="F241" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G241" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>1120010</v>
       </c>
@@ -4628,8 +5361,11 @@
       <c r="F242" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G242" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>1130020</v>
       </c>
@@ -4645,8 +5381,11 @@
       <c r="F243" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G243" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>1130010</v>
       </c>
@@ -4662,8 +5401,11 @@
       <c r="F244" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G244" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>1140020</v>
       </c>
@@ -4679,8 +5421,11 @@
       <c r="F245" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G245" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>1140010</v>
       </c>
@@ -4696,8 +5441,11 @@
       <c r="F246" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G246" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>1150020</v>
       </c>
@@ -4713,8 +5461,11 @@
       <c r="F247" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G247" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>1150010</v>
       </c>
@@ -4730,8 +5481,11 @@
       <c r="F248" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G248" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>1160020</v>
       </c>
@@ -4747,8 +5501,11 @@
       <c r="F249" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G249" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>1160010</v>
       </c>
@@ -4764,8 +5521,11 @@
       <c r="F250" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G250" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>1170020</v>
       </c>
@@ -4781,8 +5541,11 @@
       <c r="F251" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G251" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>1170010</v>
       </c>
@@ -4798,8 +5561,11 @@
       <c r="F252" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G252" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>1180020</v>
       </c>
@@ -4815,8 +5581,11 @@
       <c r="F253" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G253" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
         <v>1180010</v>
       </c>
@@ -4832,8 +5601,11 @@
       <c r="F254" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G254" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>1190020</v>
       </c>
@@ -4849,8 +5621,11 @@
       <c r="F255" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G255" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
         <v>1190010</v>
       </c>
@@ -4866,8 +5641,11 @@
       <c r="F256" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G256" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>1200020</v>
       </c>
@@ -4883,8 +5661,11 @@
       <c r="F257" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G257" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>1200010</v>
       </c>
@@ -4900,8 +5681,11 @@
       <c r="F258" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G258" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>1210020</v>
       </c>
@@ -4917,8 +5701,11 @@
       <c r="F259" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G259" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>1210010</v>
       </c>
@@ -4934,8 +5721,11 @@
       <c r="F260" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G260" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
         <v>1220020</v>
       </c>
@@ -4951,8 +5741,11 @@
       <c r="F261" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G261" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>1220010</v>
       </c>
@@ -4968,8 +5761,11 @@
       <c r="F262" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G262" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>1230020</v>
       </c>
@@ -4985,8 +5781,11 @@
       <c r="F263" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G263" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>1230010</v>
       </c>
@@ -5002,8 +5801,11 @@
       <c r="F264" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G264" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>1240020</v>
       </c>
@@ -5019,8 +5821,11 @@
       <c r="F265" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G265" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>1240010</v>
       </c>
@@ -5036,8 +5841,11 @@
       <c r="F266" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G266" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>1250020</v>
       </c>
@@ -5053,8 +5861,11 @@
       <c r="F267" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G267" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>1250010</v>
       </c>
@@ -5070,8 +5881,11 @@
       <c r="F268" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G268" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>1260020</v>
       </c>
@@ -5087,8 +5901,11 @@
       <c r="F269" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G269" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>1260010</v>
       </c>
@@ -5104,8 +5921,11 @@
       <c r="F270" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G270" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>1270020</v>
       </c>
@@ -5121,8 +5941,11 @@
       <c r="F271" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G271" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>1270010</v>
       </c>
@@ -5138,8 +5961,11 @@
       <c r="F272" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G272" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>1280020</v>
       </c>
@@ -5155,8 +5981,11 @@
       <c r="F273" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G273" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>1280010</v>
       </c>
@@ -5172,8 +6001,11 @@
       <c r="F274" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G274" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>1290020</v>
       </c>
@@ -5189,8 +6021,11 @@
       <c r="F275" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G275" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>1290010</v>
       </c>
@@ -5206,8 +6041,11 @@
       <c r="F276" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G276" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>1300020</v>
       </c>
@@ -5223,8 +6061,11 @@
       <c r="F277" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G277" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>1300010</v>
       </c>
@@ -5240,8 +6081,11 @@
       <c r="F278" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G278" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>1310020</v>
       </c>
@@ -5257,8 +6101,11 @@
       <c r="F279" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G279" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>1310010</v>
       </c>
@@ -5274,8 +6121,11 @@
       <c r="F280" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G280" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
         <v>1320020</v>
       </c>
@@ -5291,8 +6141,11 @@
       <c r="F281" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G281" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>1320010</v>
       </c>
@@ -5308,8 +6161,11 @@
       <c r="F282" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G282" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>1330020</v>
       </c>
@@ -5325,8 +6181,11 @@
       <c r="F283" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G283" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>1330010</v>
       </c>
@@ -5342,8 +6201,11 @@
       <c r="F284" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G284" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>1340020</v>
       </c>
@@ -5359,8 +6221,11 @@
       <c r="F285" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G285" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>1340010</v>
       </c>
@@ -5376,8 +6241,11 @@
       <c r="F286" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G286" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>1350020</v>
       </c>
@@ -5393,8 +6261,11 @@
       <c r="F287" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G287" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>1350010</v>
       </c>
@@ -5410,8 +6281,11 @@
       <c r="F288" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G288" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>1360020</v>
       </c>
@@ -5427,8 +6301,11 @@
       <c r="F289" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G289" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>1360010</v>
       </c>
@@ -5444,8 +6321,11 @@
       <c r="F290" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G290" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>1370020</v>
       </c>
@@ -5461,8 +6341,11 @@
       <c r="F291" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G291" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>1370010</v>
       </c>
@@ -5478,8 +6361,11 @@
       <c r="F292" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G292" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>1380020</v>
       </c>
@@ -5495,8 +6381,11 @@
       <c r="F293" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G293" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>1380010</v>
       </c>
@@ -5512,8 +6401,11 @@
       <c r="F294" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G294" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>1390020</v>
       </c>
@@ -5529,8 +6421,11 @@
       <c r="F295" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G295" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>1390010</v>
       </c>
@@ -5546,8 +6441,11 @@
       <c r="F296" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G296" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>1400020</v>
       </c>
@@ -5563,8 +6461,11 @@
       <c r="F297" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G297" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>1400010</v>
       </c>
@@ -5580,8 +6481,11 @@
       <c r="F298" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G298" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>1410020</v>
       </c>
@@ -5597,8 +6501,11 @@
       <c r="F299" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G299" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>1410010</v>
       </c>
@@ -5614,8 +6521,11 @@
       <c r="F300" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G300" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>1420020</v>
       </c>
@@ -5631,8 +6541,11 @@
       <c r="F301" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G301" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
         <v>1420010</v>
       </c>
@@ -5648,8 +6561,11 @@
       <c r="F302" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G302" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
         <v>1430020</v>
       </c>
@@ -5665,8 +6581,11 @@
       <c r="F303" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G303" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
         <v>1430010</v>
       </c>
@@ -5682,8 +6601,11 @@
       <c r="F304" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G304" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
         <v>1440020</v>
       </c>
@@ -5699,8 +6621,11 @@
       <c r="F305" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G305" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
         <v>1440010</v>
       </c>
@@ -5716,8 +6641,11 @@
       <c r="F306" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G306" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
         <v>1450020</v>
       </c>
@@ -5733,8 +6661,11 @@
       <c r="F307" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G307" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
         <v>1450010</v>
       </c>
@@ -5750,8 +6681,11 @@
       <c r="F308" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G308" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
         <v>1460020</v>
       </c>
@@ -5767,8 +6701,11 @@
       <c r="F309" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G309" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
         <v>1460010</v>
       </c>
@@ -5784,8 +6721,11 @@
       <c r="F310" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G310" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
         <v>1470020</v>
       </c>
@@ -5801,8 +6741,11 @@
       <c r="F311" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G311" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
         <v>1470010</v>
       </c>
@@ -5818,8 +6761,11 @@
       <c r="F312" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G312" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
         <v>1480020</v>
       </c>
@@ -5835,8 +6781,11 @@
       <c r="F313" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G313" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
         <v>1480010</v>
       </c>
@@ -5852,8 +6801,11 @@
       <c r="F314" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G314" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
         <v>1490020</v>
       </c>
@@ -5869,8 +6821,11 @@
       <c r="F315" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G315" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
         <v>1490010</v>
       </c>
@@ -5886,8 +6841,11 @@
       <c r="F316" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G316" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
         <v>1500020</v>
       </c>
@@ -5903,8 +6861,11 @@
       <c r="F317" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G317" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
         <v>1500010</v>
       </c>
@@ -5920,8 +6881,11 @@
       <c r="F318" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G318" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
         <v>1510020</v>
       </c>
@@ -5937,8 +6901,11 @@
       <c r="F319" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G319" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
         <v>1510010</v>
       </c>
@@ -5954,8 +6921,11 @@
       <c r="F320" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G320" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
         <v>1520020</v>
       </c>
@@ -5971,8 +6941,11 @@
       <c r="F321" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G321" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
         <v>1520010</v>
       </c>
@@ -5988,8 +6961,11 @@
       <c r="F322" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G322" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
         <v>1530020</v>
       </c>
@@ -6005,8 +6981,11 @@
       <c r="F323" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G323" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
         <v>1530010</v>
       </c>
@@ -6022,8 +7001,11 @@
       <c r="F324" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G324" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
         <v>1540020</v>
       </c>
@@ -6039,8 +7021,11 @@
       <c r="F325" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G325" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
         <v>1540010</v>
       </c>
@@ -6056,8 +7041,11 @@
       <c r="F326" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G326" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
         <v>1550020</v>
       </c>
@@ -6073,8 +7061,11 @@
       <c r="F327" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G327" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
         <v>1550010</v>
       </c>
@@ -6090,8 +7081,11 @@
       <c r="F328" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G328" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
         <v>1560020</v>
       </c>
@@ -6107,8 +7101,11 @@
       <c r="F329" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G329" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
         <v>1560010</v>
       </c>
@@ -6124,8 +7121,11 @@
       <c r="F330" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G330" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
         <v>1570020</v>
       </c>
@@ -6141,8 +7141,11 @@
       <c r="F331" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G331" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
         <v>1570010</v>
       </c>
@@ -6158,8 +7161,11 @@
       <c r="F332" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G332" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
         <v>1580020</v>
       </c>
@@ -6175,8 +7181,11 @@
       <c r="F333" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G333" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
         <v>1580010</v>
       </c>
@@ -6192,8 +7201,11 @@
       <c r="F334" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G334" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
         <v>1590020</v>
       </c>
@@ -6209,8 +7221,11 @@
       <c r="F335" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G335" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
         <v>1590010</v>
       </c>
@@ -6226,8 +7241,11 @@
       <c r="F336" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G336" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
         <v>1600020</v>
       </c>
@@ -6243,8 +7261,11 @@
       <c r="F337" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G337" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
         <v>1600010</v>
       </c>
@@ -6260,8 +7281,11 @@
       <c r="F338" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G338" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
         <v>10001</v>
       </c>
@@ -6277,8 +7301,11 @@
       <c r="F339" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G339" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
         <v>20001</v>
       </c>
@@ -6294,8 +7321,11 @@
       <c r="F340" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G340" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
         <v>30001</v>
       </c>
@@ -6311,8 +7341,11 @@
       <c r="F341" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G341" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
         <v>40001</v>
       </c>
@@ -6328,8 +7361,11 @@
       <c r="F342" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G342" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
         <v>50001</v>
       </c>
@@ -6345,8 +7381,11 @@
       <c r="F343" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G343" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
         <v>60001</v>
       </c>
@@ -6362,8 +7401,11 @@
       <c r="F344" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G344" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
         <v>70001</v>
       </c>
@@ -6379,8 +7421,11 @@
       <c r="F345" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G345" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
         <v>80001</v>
       </c>
@@ -6396,8 +7441,11 @@
       <c r="F346" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G346" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
         <v>90001</v>
       </c>
@@ -6413,8 +7461,11 @@
       <c r="F347" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G347" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
         <v>100001</v>
       </c>
@@ -6430,8 +7481,11 @@
       <c r="F348" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G348" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
         <v>110001</v>
       </c>
@@ -6447,8 +7501,11 @@
       <c r="F349" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G349" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
         <v>120001</v>
       </c>
@@ -6464,8 +7521,11 @@
       <c r="F350" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G350" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
         <v>130001</v>
       </c>
@@ -6481,8 +7541,11 @@
       <c r="F351" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G351" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
         <v>140001</v>
       </c>
@@ -6498,8 +7561,11 @@
       <c r="F352" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G352" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
         <v>150001</v>
       </c>
@@ -6515,8 +7581,11 @@
       <c r="F353" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G353" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
         <v>160001</v>
       </c>
@@ -6532,8 +7601,11 @@
       <c r="F354" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G354" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
         <v>170001</v>
       </c>
@@ -6549,8 +7621,11 @@
       <c r="F355" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G355" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
         <v>180001</v>
       </c>
@@ -6566,8 +7641,11 @@
       <c r="F356" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G356" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
         <v>190001</v>
       </c>
@@ -6583,8 +7661,11 @@
       <c r="F357" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G357" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
         <v>200001</v>
       </c>
@@ -6600,8 +7681,11 @@
       <c r="F358" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G358" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
         <v>210001</v>
       </c>
@@ -6617,8 +7701,11 @@
       <c r="F359" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G359" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
         <v>220001</v>
       </c>
@@ -6634,8 +7721,11 @@
       <c r="F360" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G360" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
         <v>230001</v>
       </c>
@@ -6651,8 +7741,11 @@
       <c r="F361" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G361" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
         <v>240001</v>
       </c>
@@ -6668,8 +7761,11 @@
       <c r="F362" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G362" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
         <v>250001</v>
       </c>
@@ -6685,8 +7781,11 @@
       <c r="F363" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G363" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
         <v>260001</v>
       </c>
@@ -6702,8 +7801,11 @@
       <c r="F364" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G364" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
         <v>270001</v>
       </c>
@@ -6719,8 +7821,11 @@
       <c r="F365" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G365" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
         <v>280001</v>
       </c>
@@ -6736,8 +7841,11 @@
       <c r="F366" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G366" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
         <v>290001</v>
       </c>
@@ -6753,8 +7861,11 @@
       <c r="F367" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G367" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
         <v>300001</v>
       </c>
@@ -6770,8 +7881,11 @@
       <c r="F368" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G368" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
         <v>310001</v>
       </c>
@@ -6787,8 +7901,11 @@
       <c r="F369" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G369" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
         <v>320001</v>
       </c>
@@ -6804,8 +7921,11 @@
       <c r="F370" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G370" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
         <v>330001</v>
       </c>
@@ -6821,8 +7941,11 @@
       <c r="F371" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G371" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
         <v>340001</v>
       </c>
@@ -6838,8 +7961,11 @@
       <c r="F372" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G372" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
         <v>350001</v>
       </c>
@@ -6855,8 +7981,11 @@
       <c r="F373" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G373" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
         <v>360001</v>
       </c>
@@ -6872,8 +8001,11 @@
       <c r="F374" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G374" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
         <v>370001</v>
       </c>
@@ -6889,8 +8021,11 @@
       <c r="F375" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G375" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
         <v>380001</v>
       </c>
@@ -6906,8 +8041,11 @@
       <c r="F376" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G376" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
         <v>390001</v>
       </c>
@@ -6923,8 +8061,11 @@
       <c r="F377" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G377" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
         <v>400001</v>
       </c>
@@ -6940,8 +8081,11 @@
       <c r="F378" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G378" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
         <v>410001</v>
       </c>
@@ -6957,8 +8101,11 @@
       <c r="F379" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G379" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
         <v>420001</v>
       </c>
@@ -6974,8 +8121,11 @@
       <c r="F380" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G380" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
         <v>430001</v>
       </c>
@@ -6991,8 +8141,11 @@
       <c r="F381" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G381" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
         <v>440001</v>
       </c>
@@ -7008,8 +8161,11 @@
       <c r="F382" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
         <v>450001</v>
       </c>
@@ -7025,8 +8181,11 @@
       <c r="F383" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G383" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
         <v>460001</v>
       </c>
@@ -7042,8 +8201,11 @@
       <c r="F384" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G384" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
         <v>470001</v>
       </c>
@@ -7059,8 +8221,11 @@
       <c r="F385" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G385" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
         <v>480001</v>
       </c>
@@ -7076,8 +8241,11 @@
       <c r="F386" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G386" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
         <v>490001</v>
       </c>
@@ -7093,8 +8261,11 @@
       <c r="F387" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G387" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
         <v>500001</v>
       </c>
@@ -7110,8 +8281,11 @@
       <c r="F388" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G388" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
         <v>510001</v>
       </c>
@@ -7127,8 +8301,11 @@
       <c r="F389" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G389" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
         <v>520001</v>
       </c>
@@ -7144,8 +8321,11 @@
       <c r="F390" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G390" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
         <v>530001</v>
       </c>
@@ -7161,8 +8341,11 @@
       <c r="F391" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G391" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
         <v>540001</v>
       </c>
@@ -7178,8 +8361,11 @@
       <c r="F392" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G392" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
         <v>550001</v>
       </c>
@@ -7195,8 +8381,11 @@
       <c r="F393" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G393" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
         <v>560001</v>
       </c>
@@ -7212,8 +8401,11 @@
       <c r="F394" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G394" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
         <v>570001</v>
       </c>
@@ -7229,8 +8421,11 @@
       <c r="F395" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G395" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
         <v>580001</v>
       </c>
@@ -7246,8 +8441,11 @@
       <c r="F396" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G396" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
         <v>590001</v>
       </c>
@@ -7263,8 +8461,11 @@
       <c r="F397" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G397" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
         <v>600001</v>
       </c>
@@ -7280,8 +8481,11 @@
       <c r="F398" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G398" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
         <v>610001</v>
       </c>
@@ -7297,8 +8501,11 @@
       <c r="F399" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G399" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
         <v>620001</v>
       </c>
@@ -7314,8 +8521,11 @@
       <c r="F400" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G400" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
         <v>630001</v>
       </c>
@@ -7331,8 +8541,11 @@
       <c r="F401" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G401" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
         <v>640001</v>
       </c>
@@ -7348,8 +8561,11 @@
       <c r="F402" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G402" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
         <v>650001</v>
       </c>
@@ -7365,8 +8581,11 @@
       <c r="F403" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G403" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
         <v>660001</v>
       </c>
@@ -7382,8 +8601,11 @@
       <c r="F404" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G404" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
         <v>670001</v>
       </c>
@@ -7399,8 +8621,11 @@
       <c r="F405" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G405" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
         <v>680001</v>
       </c>
@@ -7416,8 +8641,11 @@
       <c r="F406" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G406" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
         <v>690001</v>
       </c>
@@ -7433,8 +8661,11 @@
       <c r="F407" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G407" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
         <v>700001</v>
       </c>
@@ -7450,8 +8681,11 @@
       <c r="F408" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G408" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
         <v>710001</v>
       </c>
@@ -7467,8 +8701,11 @@
       <c r="F409" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G409" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
         <v>720001</v>
       </c>
@@ -7484,8 +8721,11 @@
       <c r="F410" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G410" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
         <v>730001</v>
       </c>
@@ -7501,8 +8741,11 @@
       <c r="F411" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G411" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
         <v>740001</v>
       </c>
@@ -7518,8 +8761,11 @@
       <c r="F412" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G412" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
         <v>750001</v>
       </c>
@@ -7535,8 +8781,11 @@
       <c r="F413" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G413" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
         <v>760001</v>
       </c>
@@ -7552,8 +8801,11 @@
       <c r="F414" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G414" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
         <v>770001</v>
       </c>
@@ -7569,8 +8821,11 @@
       <c r="F415" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G415" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
         <v>780001</v>
       </c>
@@ -7586,8 +8841,11 @@
       <c r="F416" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G416" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
         <v>790001</v>
       </c>
@@ -7603,8 +8861,11 @@
       <c r="F417" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G417" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
         <v>800001</v>
       </c>
@@ -7620,8 +8881,11 @@
       <c r="F418" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G418" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
         <v>810001</v>
       </c>
@@ -7637,8 +8901,11 @@
       <c r="F419" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G419" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
         <v>820001</v>
       </c>
@@ -7654,8 +8921,11 @@
       <c r="F420" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G420" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
         <v>830001</v>
       </c>
@@ -7671,8 +8941,11 @@
       <c r="F421" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G421" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
         <v>840001</v>
       </c>
@@ -7688,8 +8961,11 @@
       <c r="F422" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G422" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
         <v>850001</v>
       </c>
@@ -7705,8 +8981,11 @@
       <c r="F423" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G423" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
         <v>860001</v>
       </c>
@@ -7722,8 +9001,11 @@
       <c r="F424" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G424" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
         <v>870001</v>
       </c>
@@ -7739,8 +9021,11 @@
       <c r="F425" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G425" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
         <v>880001</v>
       </c>
@@ -7756,8 +9041,11 @@
       <c r="F426" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G426" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
         <v>890001</v>
       </c>
@@ -7773,8 +9061,11 @@
       <c r="F427" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G427" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
         <v>900001</v>
       </c>
@@ -7790,8 +9081,11 @@
       <c r="F428" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G428" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
         <v>910001</v>
       </c>
@@ -7807,8 +9101,11 @@
       <c r="F429" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G429" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
         <v>920001</v>
       </c>
@@ -7824,8 +9121,11 @@
       <c r="F430" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G430" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
         <v>930001</v>
       </c>
@@ -7841,8 +9141,11 @@
       <c r="F431" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G431" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
         <v>940001</v>
       </c>
@@ -7858,8 +9161,11 @@
       <c r="F432" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
         <v>950001</v>
       </c>
@@ -7875,8 +9181,11 @@
       <c r="F433" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G433" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
         <v>960001</v>
       </c>
@@ -7892,8 +9201,11 @@
       <c r="F434" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G434" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
         <v>970001</v>
       </c>
@@ -7909,8 +9221,11 @@
       <c r="F435" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G435" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
         <v>980001</v>
       </c>
@@ -7926,8 +9241,11 @@
       <c r="F436" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G436" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
         <v>990001</v>
       </c>
@@ -7943,8 +9261,11 @@
       <c r="F437" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G437" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
         <v>1000001</v>
       </c>
@@ -7960,8 +9281,11 @@
       <c r="F438" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G438" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
         <v>1010001</v>
       </c>
@@ -7977,8 +9301,11 @@
       <c r="F439" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G439" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
         <v>1020001</v>
       </c>
@@ -7994,8 +9321,11 @@
       <c r="F440" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G440" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
         <v>1030001</v>
       </c>
@@ -8011,8 +9341,11 @@
       <c r="F441" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G441" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
         <v>1040001</v>
       </c>
@@ -8028,8 +9361,11 @@
       <c r="F442" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G442" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
         <v>1050001</v>
       </c>
@@ -8045,8 +9381,11 @@
       <c r="F443" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G443" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
         <v>1060001</v>
       </c>
@@ -8062,8 +9401,11 @@
       <c r="F444" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G444" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
         <v>1070001</v>
       </c>
@@ -8079,8 +9421,11 @@
       <c r="F445" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G445" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
         <v>1080001</v>
       </c>
@@ -8096,8 +9441,11 @@
       <c r="F446" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G446" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
         <v>1090001</v>
       </c>
@@ -8113,8 +9461,11 @@
       <c r="F447" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G447" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
         <v>1100001</v>
       </c>
@@ -8130,8 +9481,11 @@
       <c r="F448" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G448" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
         <v>1110001</v>
       </c>
@@ -8147,8 +9501,11 @@
       <c r="F449" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G449" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
         <v>1120001</v>
       </c>
@@ -8164,8 +9521,11 @@
       <c r="F450" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G450" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
         <v>1130001</v>
       </c>
@@ -8181,8 +9541,11 @@
       <c r="F451" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G451" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
         <v>1140001</v>
       </c>
@@ -8198,8 +9561,11 @@
       <c r="F452" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G452" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
         <v>1150001</v>
       </c>
@@ -8215,8 +9581,11 @@
       <c r="F453" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G453" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
         <v>1160001</v>
       </c>
@@ -8232,8 +9601,11 @@
       <c r="F454" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G454" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
         <v>1170001</v>
       </c>
@@ -8249,8 +9621,11 @@
       <c r="F455" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G455" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
         <v>1180001</v>
       </c>
@@ -8266,8 +9641,11 @@
       <c r="F456" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G456" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
         <v>1190001</v>
       </c>
@@ -8283,8 +9661,11 @@
       <c r="F457" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G457" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
         <v>1200001</v>
       </c>
@@ -8300,8 +9681,11 @@
       <c r="F458" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G458" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
         <v>1210001</v>
       </c>
@@ -8317,8 +9701,11 @@
       <c r="F459" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G459" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
         <v>1220001</v>
       </c>
@@ -8334,8 +9721,11 @@
       <c r="F460" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G460" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
         <v>1230001</v>
       </c>
@@ -8351,8 +9741,11 @@
       <c r="F461" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G461" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
         <v>1240001</v>
       </c>
@@ -8368,8 +9761,11 @@
       <c r="F462" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G462" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
         <v>1250001</v>
       </c>
@@ -8385,8 +9781,11 @@
       <c r="F463" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G463" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
         <v>1260001</v>
       </c>
@@ -8402,8 +9801,11 @@
       <c r="F464" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G464" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
         <v>1270001</v>
       </c>
@@ -8419,8 +9821,11 @@
       <c r="F465" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G465" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
         <v>1280001</v>
       </c>
@@ -8436,8 +9841,11 @@
       <c r="F466" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G466" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
         <v>1290001</v>
       </c>
@@ -8453,8 +9861,11 @@
       <c r="F467" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G467" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
         <v>1300001</v>
       </c>
@@ -8470,8 +9881,11 @@
       <c r="F468" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G468" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
         <v>1310001</v>
       </c>
@@ -8487,8 +9901,11 @@
       <c r="F469" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G469" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
         <v>1320001</v>
       </c>
@@ -8504,8 +9921,11 @@
       <c r="F470" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G470" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
         <v>1330001</v>
       </c>
@@ -8521,8 +9941,11 @@
       <c r="F471" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G471" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
         <v>1340001</v>
       </c>
@@ -8538,8 +9961,11 @@
       <c r="F472" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G472" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
         <v>1350001</v>
       </c>
@@ -8555,8 +9981,11 @@
       <c r="F473" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G473" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
         <v>1360001</v>
       </c>
@@ -8572,8 +10001,11 @@
       <c r="F474" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G474" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
         <v>1370001</v>
       </c>
@@ -8589,8 +10021,11 @@
       <c r="F475" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G475" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
         <v>1380001</v>
       </c>
@@ -8606,8 +10041,11 @@
       <c r="F476" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G476" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
         <v>1390001</v>
       </c>
@@ -8623,8 +10061,11 @@
       <c r="F477" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G477" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
         <v>1400001</v>
       </c>
@@ -8640,8 +10081,11 @@
       <c r="F478" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G478" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
         <v>1410001</v>
       </c>
@@ -8657,8 +10101,11 @@
       <c r="F479" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G479" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
         <v>1420001</v>
       </c>
@@ -8674,8 +10121,11 @@
       <c r="F480" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G480" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
         <v>1430001</v>
       </c>
@@ -8691,8 +10141,11 @@
       <c r="F481" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G481" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
         <v>1440001</v>
       </c>
@@ -8708,8 +10161,11 @@
       <c r="F482" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G482" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
         <v>1450001</v>
       </c>
@@ -8725,8 +10181,11 @@
       <c r="F483" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G483" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
         <v>1460001</v>
       </c>
@@ -8742,8 +10201,11 @@
       <c r="F484" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G484" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
         <v>1470001</v>
       </c>
@@ -8759,8 +10221,11 @@
       <c r="F485" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G485" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
         <v>1480001</v>
       </c>
@@ -8776,8 +10241,11 @@
       <c r="F486" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G486" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
         <v>1490001</v>
       </c>
@@ -8793,8 +10261,11 @@
       <c r="F487" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G487" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A488" s="1">
         <v>1500001</v>
       </c>
@@ -8810,8 +10281,11 @@
       <c r="F488" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G488" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A489" s="1">
         <v>1510001</v>
       </c>
@@ -8827,8 +10301,11 @@
       <c r="F489" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G489" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A490" s="1">
         <v>1520001</v>
       </c>
@@ -8844,8 +10321,11 @@
       <c r="F490" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G490" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A491" s="1">
         <v>1530001</v>
       </c>
@@ -8861,8 +10341,11 @@
       <c r="F491" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G491" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A492" s="1">
         <v>1540001</v>
       </c>
@@ -8878,8 +10361,11 @@
       <c r="F492" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G492" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A493" s="1">
         <v>1550001</v>
       </c>
@@ -8895,8 +10381,11 @@
       <c r="F493" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G493" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A494" s="1">
         <v>1560001</v>
       </c>
@@ -8912,8 +10401,11 @@
       <c r="F494" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G494" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A495" s="1">
         <v>1570001</v>
       </c>
@@ -8929,8 +10421,11 @@
       <c r="F495" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G495" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A496" s="1">
         <v>1580001</v>
       </c>
@@ -8946,8 +10441,11 @@
       <c r="F496" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G496" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A497" s="1">
         <v>1590001</v>
       </c>
@@ -8963,8 +10461,11 @@
       <c r="F497" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G497" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A498" s="1">
         <v>1600001</v>
       </c>
@@ -8979,6 +10480,9 @@
       </c>
       <c r="F498" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="G498" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A5526B-7FCE-4A3D-9D40-2DFC3E3F8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E50B5D7-20E8-4750-AF83-A65CC1840123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="43">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -150,21 +150,6 @@
     <t>46200001:80</t>
   </si>
   <si>
-    <t>46700001:17</t>
-  </si>
-  <si>
-    <t>46200001:100</t>
-  </si>
-  <si>
-    <t>46700001:15</t>
-  </si>
-  <si>
-    <t>46200001:120</t>
-  </si>
-  <si>
-    <t>46700001:18</t>
-  </si>
-  <si>
     <t>add_kongfu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,6 +159,34 @@
   </si>
   <si>
     <t>增加通关值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300006:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300003:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300004:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300002:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300005:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +569,7 @@
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
@@ -579,7 +592,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
@@ -602,7 +615,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
@@ -1039,7 +1052,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -1059,10 +1072,10 @@
         <v>20</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G27" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
@@ -1079,10 +1092,10 @@
         <v>20</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G28" s="1">
-        <v>200</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
@@ -1099,10 +1112,10 @@
         <v>20</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G29" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
@@ -1119,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G30" s="1">
         <v>400</v>
@@ -1139,10 +1152,10 @@
         <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G31" s="1">
-        <v>500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
@@ -1159,10 +1172,10 @@
         <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G32" s="1">
-        <v>600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9DF0DC-9B63-455B-9C0A-C52ED26CDA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EC69D2-95A2-4F0B-B00C-1DD279E27D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="71">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -226,6 +226,63 @@
   <si>
     <t>drop_exp_num</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:2</t>
+  </si>
+  <si>
+    <t>42617001</t>
+  </si>
+  <si>
+    <t>48300003:1</t>
+  </si>
+  <si>
+    <t>46700001:1</t>
+  </si>
+  <si>
+    <t>42633001</t>
+  </si>
+  <si>
+    <t>46700001:2</t>
+  </si>
+  <si>
+    <t>48300005:1</t>
+  </si>
+  <si>
+    <t>42614001</t>
+  </si>
+  <si>
+    <t>42731001</t>
+  </si>
+  <si>
+    <t>48200001:1</t>
+  </si>
+  <si>
+    <t>42636001</t>
+  </si>
+  <si>
+    <t>48300004:1</t>
+  </si>
+  <si>
+    <t>46200001:3</t>
+  </si>
+  <si>
+    <t>46700001:3</t>
+  </si>
+  <si>
+    <t>42635001</t>
+  </si>
+  <si>
+    <t>48300002:1</t>
+  </si>
+  <si>
+    <t>42654001</t>
+  </si>
+  <si>
+    <t>48300006:1</t>
+  </si>
+  <si>
+    <t>42656001</t>
   </si>
 </sst>
 </file>
@@ -1534,8 +1591,8 @@
       <c r="B34" s="1">
         <v>8</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
+      <c r="D34" s="2">
+        <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>16</v>
@@ -1563,8 +1620,8 @@
       <c r="B35" s="1">
         <v>8</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
+      <c r="D35" s="2">
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>16</v>
@@ -1616,10 +1673,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>90001</v>
+        <v>100020</v>
       </c>
       <c r="B37" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
@@ -1631,7 +1688,7 @@
         <v>17</v>
       </c>
       <c r="G37" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -1645,10 +1702,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>90002</v>
+        <v>100010</v>
       </c>
       <c r="B38" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1660,7 +1717,7 @@
         <v>17</v>
       </c>
       <c r="G38" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -1674,10 +1731,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>90003</v>
+        <v>110020</v>
       </c>
       <c r="B39" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1689,7 +1746,7 @@
         <v>17</v>
       </c>
       <c r="G39" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -1703,10 +1760,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>90004</v>
+        <v>110010</v>
       </c>
       <c r="B40" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -1718,7 +1775,7 @@
         <v>17</v>
       </c>
       <c r="G40" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -1732,10 +1789,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>90005</v>
+        <v>110001</v>
       </c>
       <c r="B41" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
@@ -1744,13 +1801,13 @@
         <v>16</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G41" s="1">
-        <v>80</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>16</v>
@@ -1761,10 +1818,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>90006</v>
+        <v>110002</v>
       </c>
       <c r="B42" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
@@ -1773,10 +1830,10 @@
         <v>16</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G42" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -1785,15 +1842,15 @@
         <v>16</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>90007</v>
+        <v>110003</v>
       </c>
       <c r="B43" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -1802,13 +1859,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G43" s="1">
-        <v>120</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>16</v>
@@ -1819,10 +1876,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>90008</v>
+        <v>110004</v>
       </c>
       <c r="B44" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
@@ -1831,10 +1888,10 @@
         <v>16</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G44" s="1">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -1843,15 +1900,15 @@
         <v>16</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>90009</v>
+        <v>110005</v>
       </c>
       <c r="B45" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
@@ -1860,10 +1917,10 @@
         <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G45" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -1872,15 +1929,15 @@
         <v>16</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>90011</v>
+        <v>110006</v>
       </c>
       <c r="B46" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
@@ -1889,13 +1946,13 @@
         <v>16</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G46" s="1">
-        <v>250</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>16</v>
@@ -1906,10 +1963,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>90012</v>
+        <v>110007</v>
       </c>
       <c r="B47" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
@@ -1918,10 +1975,10 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G47" s="1">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -1930,15 +1987,15 @@
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>90013</v>
+        <v>110008</v>
       </c>
       <c r="B48" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
@@ -1947,13 +2004,13 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G48" s="1">
-        <v>500</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>16</v>
@@ -1964,10 +2021,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>90014</v>
+        <v>110009</v>
       </c>
       <c r="B49" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
@@ -1976,10 +2033,10 @@
         <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G49" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -1988,15 +2045,15 @@
         <v>16</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>90015</v>
+        <v>110011</v>
       </c>
       <c r="B50" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -2005,13 +2062,13 @@
         <v>16</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G50" s="1">
-        <v>900</v>
-      </c>
-      <c r="H50" s="2">
-        <v>0</v>
+        <v>250</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
@@ -2022,10 +2079,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>90016</v>
+        <v>110012</v>
       </c>
       <c r="B51" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
@@ -2034,10 +2091,10 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G51" s="1">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2046,15 +2103,15 @@
         <v>16</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>90017</v>
+        <v>110013</v>
       </c>
       <c r="B52" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
@@ -2063,10 +2120,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G52" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2075,15 +2132,15 @@
         <v>16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>90018</v>
+        <v>110014</v>
       </c>
       <c r="B53" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -2092,13 +2149,13 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G53" s="1">
-        <v>1800</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>16</v>
@@ -2109,10 +2166,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>90021</v>
+        <v>110015</v>
       </c>
       <c r="B54" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
@@ -2121,10 +2178,10 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="G54" s="1">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2133,15 +2190,15 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>90019</v>
+        <v>110016</v>
       </c>
       <c r="B55" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
@@ -2150,10 +2207,10 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G55" s="1">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2162,15 +2219,15 @@
         <v>16</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>90023</v>
+        <v>110017</v>
       </c>
       <c r="B56" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
@@ -2179,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G56" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H56" s="2">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>16</v>
@@ -2196,10 +2253,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>90022</v>
+        <v>110018</v>
       </c>
       <c r="B57" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -2208,10 +2265,10 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G57" s="1">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2220,15 +2277,15 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>90024</v>
+        <v>110021</v>
       </c>
       <c r="B58" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -2237,10 +2294,10 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G58" s="1">
-        <v>5600</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2249,27 +2306,27 @@
         <v>16</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>100020</v>
+        <v>110019</v>
       </c>
       <c r="B59" s="1">
-        <v>10</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2278,30 +2335,30 @@
         <v>16</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>100010</v>
+        <v>110023</v>
       </c>
       <c r="B60" s="1">
-        <v>10</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>16</v>
@@ -2312,22 +2369,22 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110020</v>
+        <v>110022</v>
       </c>
       <c r="B61" s="1">
         <v>11</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>10</v>
+      <c r="D61" s="2">
+        <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -2336,27 +2393,27 @@
         <v>16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>110010</v>
+        <v>110024</v>
       </c>
       <c r="B62" s="1">
         <v>11</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>10</v>
+      <c r="D62" s="2">
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -2365,7 +2422,7 @@
         <v>16</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EC69D2-95A2-4F0B-B00C-1DD279E27D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A8338-A449-4842-AE72-FC16A71DED26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$J$360</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="74">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -240,9 +243,6 @@
     <t>46700001:1</t>
   </si>
   <si>
-    <t>42633001</t>
-  </si>
-  <si>
     <t>46700001:2</t>
   </si>
   <si>
@@ -258,12 +258,6 @@
     <t>48200001:1</t>
   </si>
   <si>
-    <t>42636001</t>
-  </si>
-  <si>
-    <t>48300004:1</t>
-  </si>
-  <si>
     <t>46200001:3</t>
   </si>
   <si>
@@ -273,16 +267,34 @@
     <t>42635001</t>
   </si>
   <si>
-    <t>48300002:1</t>
-  </si>
-  <si>
     <t>42654001</t>
   </si>
   <si>
-    <t>48300006:1</t>
+    <t>42656001</t>
   </si>
   <si>
-    <t>42656001</t>
+    <t>42613001</t>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>48200004:1</t>
+  </si>
+  <si>
+    <t>46700001:2_48300001:1</t>
+  </si>
+  <si>
+    <t>48200006:1</t>
+  </si>
+  <si>
+    <t>42653001</t>
+  </si>
+  <si>
+    <t>46700001:1_48300001:1</t>
+  </si>
+  <si>
+    <t>46700001:5_48300001:1</t>
   </si>
 </sst>
 </file>
@@ -626,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J520"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1833,7 +1845,7 @@
         <v>54</v>
       </c>
       <c r="G42" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -1859,13 +1871,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G43" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>16</v>
@@ -1888,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G44" s="1">
         <v>70</v>
@@ -1917,10 +1929,10 @@
         <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G45" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -1929,7 +1941,7 @@
         <v>16</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
@@ -1949,10 +1961,10 @@
         <v>52</v>
       </c>
       <c r="G46" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>16</v>
@@ -1975,19 +1987,19 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G47" s="1">
-        <v>120</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
@@ -2004,19 +2016,19 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G48" s="1">
-        <v>150</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>60</v>
+        <v>250</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
@@ -2033,10 +2045,10 @@
         <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G49" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -2045,7 +2057,7 @@
         <v>16</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
@@ -2062,19 +2074,19 @@
         <v>16</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G50" s="1">
-        <v>250</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>62</v>
+        <v>500</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.15">
@@ -2091,19 +2103,19 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G51" s="1">
+        <v>600</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G51" s="1">
-        <v>300</v>
-      </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
       <c r="I51" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
@@ -2120,10 +2132,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2132,7 +2144,7 @@
         <v>16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
@@ -2149,13 +2161,13 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G53" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>16</v>
@@ -2178,10 +2190,10 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G54" s="1">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2190,7 +2202,7 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
@@ -2207,10 +2219,10 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G55" s="1">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2219,7 +2231,7 @@
         <v>16</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
@@ -2236,19 +2248,19 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G56" s="1">
-        <v>1500</v>
-      </c>
-      <c r="H56" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
@@ -2268,7 +2280,7 @@
         <v>61</v>
       </c>
       <c r="G57" s="1">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2277,12 +2289,12 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>110021</v>
+        <v>110019</v>
       </c>
       <c r="B58" s="1">
         <v>11</v>
@@ -2294,24 +2306,24 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G58" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H58" s="2">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>110019</v>
+        <v>110021</v>
       </c>
       <c r="B59" s="1">
         <v>11</v>
@@ -2323,10 +2335,10 @@
         <v>16</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G59" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2335,12 +2347,12 @@
         <v>16</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>110023</v>
+        <v>110022</v>
       </c>
       <c r="B60" s="1">
         <v>11</v>
@@ -2352,13 +2364,13 @@
         <v>16</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G60" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>16</v>
@@ -2369,7 +2381,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110022</v>
+        <v>110023</v>
       </c>
       <c r="B61" s="1">
         <v>11</v>
@@ -2381,10 +2393,10 @@
         <v>16</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G61" s="1">
-        <v>3500</v>
+        <v>8000</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -2393,7 +2405,7 @@
         <v>16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">
@@ -2410,10 +2422,10 @@
         <v>16</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G62" s="1">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -2422,7 +2434,7 @@
         <v>16</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.15">
@@ -11064,4646 +11076,6 @@
         <v>16</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A361" s="1">
-        <v>10001</v>
-      </c>
-      <c r="B361" s="1">
-        <v>1</v>
-      </c>
-      <c r="D361" s="1">
-        <v>0</v>
-      </c>
-      <c r="E361" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F361" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G361" s="1">
-        <v>0</v>
-      </c>
-      <c r="H361" s="2">
-        <v>0</v>
-      </c>
-      <c r="I361" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J361" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A362" s="1">
-        <v>20001</v>
-      </c>
-      <c r="B362" s="1">
-        <v>2</v>
-      </c>
-      <c r="D362" s="1">
-        <v>0</v>
-      </c>
-      <c r="E362" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F362" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G362" s="1">
-        <v>0</v>
-      </c>
-      <c r="H362" s="2">
-        <v>0</v>
-      </c>
-      <c r="I362" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J362" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A363" s="1">
-        <v>30001</v>
-      </c>
-      <c r="B363" s="1">
-        <v>3</v>
-      </c>
-      <c r="D363" s="1">
-        <v>0</v>
-      </c>
-      <c r="E363" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F363" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G363" s="1">
-        <v>0</v>
-      </c>
-      <c r="H363" s="2">
-        <v>0</v>
-      </c>
-      <c r="I363" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J363" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A364" s="1">
-        <v>40001</v>
-      </c>
-      <c r="B364" s="1">
-        <v>4</v>
-      </c>
-      <c r="D364" s="1">
-        <v>0</v>
-      </c>
-      <c r="E364" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F364" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G364" s="1">
-        <v>0</v>
-      </c>
-      <c r="H364" s="2">
-        <v>0</v>
-      </c>
-      <c r="I364" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J364" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A365" s="1">
-        <v>50001</v>
-      </c>
-      <c r="B365" s="1">
-        <v>5</v>
-      </c>
-      <c r="D365" s="1">
-        <v>0</v>
-      </c>
-      <c r="E365" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F365" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G365" s="1">
-        <v>0</v>
-      </c>
-      <c r="H365" s="2">
-        <v>0</v>
-      </c>
-      <c r="I365" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J365" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A366" s="1">
-        <v>60001</v>
-      </c>
-      <c r="B366" s="1">
-        <v>6</v>
-      </c>
-      <c r="D366" s="1">
-        <v>0</v>
-      </c>
-      <c r="E366" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F366" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G366" s="1">
-        <v>0</v>
-      </c>
-      <c r="H366" s="2">
-        <v>0</v>
-      </c>
-      <c r="I366" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J366" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A367" s="1">
-        <v>70001</v>
-      </c>
-      <c r="B367" s="1">
-        <v>7</v>
-      </c>
-      <c r="D367" s="1">
-        <v>0</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F367" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G367" s="1">
-        <v>0</v>
-      </c>
-      <c r="H367" s="2">
-        <v>0</v>
-      </c>
-      <c r="I367" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J367" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A368" s="1">
-        <v>80001</v>
-      </c>
-      <c r="B368" s="1">
-        <v>8</v>
-      </c>
-      <c r="D368" s="1">
-        <v>0</v>
-      </c>
-      <c r="E368" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F368" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G368" s="1">
-        <v>0</v>
-      </c>
-      <c r="H368" s="2">
-        <v>0</v>
-      </c>
-      <c r="I368" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J368" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A369" s="1">
-        <v>90001</v>
-      </c>
-      <c r="B369" s="1">
-        <v>9</v>
-      </c>
-      <c r="D369" s="1">
-        <v>0</v>
-      </c>
-      <c r="E369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F369" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G369" s="1">
-        <v>0</v>
-      </c>
-      <c r="H369" s="2">
-        <v>0</v>
-      </c>
-      <c r="I369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J369" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A370" s="1">
-        <v>100001</v>
-      </c>
-      <c r="B370" s="1">
-        <v>10</v>
-      </c>
-      <c r="D370" s="1">
-        <v>0</v>
-      </c>
-      <c r="E370" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F370" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G370" s="1">
-        <v>0</v>
-      </c>
-      <c r="H370" s="2">
-        <v>0</v>
-      </c>
-      <c r="I370" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J370" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A371" s="1">
-        <v>110001</v>
-      </c>
-      <c r="B371" s="1">
-        <v>11</v>
-      </c>
-      <c r="D371" s="1">
-        <v>0</v>
-      </c>
-      <c r="E371" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F371" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G371" s="1">
-        <v>0</v>
-      </c>
-      <c r="H371" s="2">
-        <v>0</v>
-      </c>
-      <c r="I371" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J371" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A372" s="1">
-        <v>120001</v>
-      </c>
-      <c r="B372" s="1">
-        <v>12</v>
-      </c>
-      <c r="D372" s="1">
-        <v>0</v>
-      </c>
-      <c r="E372" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F372" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G372" s="1">
-        <v>0</v>
-      </c>
-      <c r="H372" s="2">
-        <v>0</v>
-      </c>
-      <c r="I372" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J372" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A373" s="1">
-        <v>130001</v>
-      </c>
-      <c r="B373" s="1">
-        <v>13</v>
-      </c>
-      <c r="D373" s="1">
-        <v>0</v>
-      </c>
-      <c r="E373" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F373" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G373" s="1">
-        <v>0</v>
-      </c>
-      <c r="H373" s="2">
-        <v>0</v>
-      </c>
-      <c r="I373" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J373" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A374" s="1">
-        <v>140001</v>
-      </c>
-      <c r="B374" s="1">
-        <v>14</v>
-      </c>
-      <c r="D374" s="1">
-        <v>0</v>
-      </c>
-      <c r="E374" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F374" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G374" s="1">
-        <v>0</v>
-      </c>
-      <c r="H374" s="2">
-        <v>0</v>
-      </c>
-      <c r="I374" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J374" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A375" s="1">
-        <v>150001</v>
-      </c>
-      <c r="B375" s="1">
-        <v>15</v>
-      </c>
-      <c r="D375" s="1">
-        <v>0</v>
-      </c>
-      <c r="E375" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F375" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G375" s="1">
-        <v>0</v>
-      </c>
-      <c r="H375" s="2">
-        <v>0</v>
-      </c>
-      <c r="I375" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J375" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A376" s="1">
-        <v>160001</v>
-      </c>
-      <c r="B376" s="1">
-        <v>16</v>
-      </c>
-      <c r="D376" s="1">
-        <v>0</v>
-      </c>
-      <c r="E376" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F376" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G376" s="1">
-        <v>0</v>
-      </c>
-      <c r="H376" s="2">
-        <v>0</v>
-      </c>
-      <c r="I376" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J376" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A377" s="1">
-        <v>170001</v>
-      </c>
-      <c r="B377" s="1">
-        <v>17</v>
-      </c>
-      <c r="D377" s="1">
-        <v>0</v>
-      </c>
-      <c r="E377" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F377" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G377" s="1">
-        <v>0</v>
-      </c>
-      <c r="H377" s="2">
-        <v>0</v>
-      </c>
-      <c r="I377" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J377" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A378" s="1">
-        <v>180001</v>
-      </c>
-      <c r="B378" s="1">
-        <v>18</v>
-      </c>
-      <c r="D378" s="1">
-        <v>0</v>
-      </c>
-      <c r="E378" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F378" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G378" s="1">
-        <v>0</v>
-      </c>
-      <c r="H378" s="2">
-        <v>0</v>
-      </c>
-      <c r="I378" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J378" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A379" s="1">
-        <v>190001</v>
-      </c>
-      <c r="B379" s="1">
-        <v>19</v>
-      </c>
-      <c r="D379" s="1">
-        <v>0</v>
-      </c>
-      <c r="E379" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F379" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G379" s="1">
-        <v>0</v>
-      </c>
-      <c r="H379" s="2">
-        <v>0</v>
-      </c>
-      <c r="I379" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J379" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A380" s="1">
-        <v>200001</v>
-      </c>
-      <c r="B380" s="1">
-        <v>20</v>
-      </c>
-      <c r="D380" s="1">
-        <v>0</v>
-      </c>
-      <c r="E380" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F380" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G380" s="1">
-        <v>0</v>
-      </c>
-      <c r="H380" s="2">
-        <v>0</v>
-      </c>
-      <c r="I380" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J380" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A381" s="1">
-        <v>210001</v>
-      </c>
-      <c r="B381" s="1">
-        <v>21</v>
-      </c>
-      <c r="D381" s="1">
-        <v>0</v>
-      </c>
-      <c r="E381" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F381" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G381" s="1">
-        <v>0</v>
-      </c>
-      <c r="H381" s="2">
-        <v>0</v>
-      </c>
-      <c r="I381" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J381" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A382" s="1">
-        <v>220001</v>
-      </c>
-      <c r="B382" s="1">
-        <v>22</v>
-      </c>
-      <c r="D382" s="1">
-        <v>0</v>
-      </c>
-      <c r="E382" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F382" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G382" s="1">
-        <v>0</v>
-      </c>
-      <c r="H382" s="2">
-        <v>0</v>
-      </c>
-      <c r="I382" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J382" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A383" s="1">
-        <v>230001</v>
-      </c>
-      <c r="B383" s="1">
-        <v>23</v>
-      </c>
-      <c r="D383" s="1">
-        <v>0</v>
-      </c>
-      <c r="E383" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F383" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G383" s="1">
-        <v>0</v>
-      </c>
-      <c r="H383" s="2">
-        <v>0</v>
-      </c>
-      <c r="I383" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J383" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A384" s="1">
-        <v>240001</v>
-      </c>
-      <c r="B384" s="1">
-        <v>24</v>
-      </c>
-      <c r="D384" s="1">
-        <v>0</v>
-      </c>
-      <c r="E384" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F384" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G384" s="1">
-        <v>0</v>
-      </c>
-      <c r="H384" s="2">
-        <v>0</v>
-      </c>
-      <c r="I384" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J384" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A385" s="1">
-        <v>250001</v>
-      </c>
-      <c r="B385" s="1">
-        <v>25</v>
-      </c>
-      <c r="D385" s="1">
-        <v>0</v>
-      </c>
-      <c r="E385" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F385" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G385" s="1">
-        <v>0</v>
-      </c>
-      <c r="H385" s="2">
-        <v>0</v>
-      </c>
-      <c r="I385" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J385" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A386" s="1">
-        <v>260001</v>
-      </c>
-      <c r="B386" s="1">
-        <v>26</v>
-      </c>
-      <c r="D386" s="1">
-        <v>0</v>
-      </c>
-      <c r="E386" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F386" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G386" s="1">
-        <v>0</v>
-      </c>
-      <c r="H386" s="2">
-        <v>0</v>
-      </c>
-      <c r="I386" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J386" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A387" s="1">
-        <v>270001</v>
-      </c>
-      <c r="B387" s="1">
-        <v>27</v>
-      </c>
-      <c r="D387" s="1">
-        <v>0</v>
-      </c>
-      <c r="E387" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F387" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G387" s="1">
-        <v>0</v>
-      </c>
-      <c r="H387" s="2">
-        <v>0</v>
-      </c>
-      <c r="I387" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J387" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A388" s="1">
-        <v>280001</v>
-      </c>
-      <c r="B388" s="1">
-        <v>28</v>
-      </c>
-      <c r="D388" s="1">
-        <v>0</v>
-      </c>
-      <c r="E388" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F388" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G388" s="1">
-        <v>0</v>
-      </c>
-      <c r="H388" s="2">
-        <v>0</v>
-      </c>
-      <c r="I388" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J388" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A389" s="1">
-        <v>290001</v>
-      </c>
-      <c r="B389" s="1">
-        <v>29</v>
-      </c>
-      <c r="D389" s="1">
-        <v>0</v>
-      </c>
-      <c r="E389" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F389" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G389" s="1">
-        <v>0</v>
-      </c>
-      <c r="H389" s="2">
-        <v>0</v>
-      </c>
-      <c r="I389" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J389" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A390" s="1">
-        <v>300001</v>
-      </c>
-      <c r="B390" s="1">
-        <v>30</v>
-      </c>
-      <c r="D390" s="1">
-        <v>0</v>
-      </c>
-      <c r="E390" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F390" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G390" s="1">
-        <v>0</v>
-      </c>
-      <c r="H390" s="2">
-        <v>0</v>
-      </c>
-      <c r="I390" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J390" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A391" s="1">
-        <v>310001</v>
-      </c>
-      <c r="B391" s="1">
-        <v>31</v>
-      </c>
-      <c r="D391" s="1">
-        <v>0</v>
-      </c>
-      <c r="E391" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F391" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G391" s="1">
-        <v>0</v>
-      </c>
-      <c r="H391" s="2">
-        <v>0</v>
-      </c>
-      <c r="I391" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J391" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A392" s="1">
-        <v>320001</v>
-      </c>
-      <c r="B392" s="1">
-        <v>32</v>
-      </c>
-      <c r="D392" s="1">
-        <v>0</v>
-      </c>
-      <c r="E392" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F392" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G392" s="1">
-        <v>0</v>
-      </c>
-      <c r="H392" s="2">
-        <v>0</v>
-      </c>
-      <c r="I392" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J392" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A393" s="1">
-        <v>330001</v>
-      </c>
-      <c r="B393" s="1">
-        <v>33</v>
-      </c>
-      <c r="D393" s="1">
-        <v>0</v>
-      </c>
-      <c r="E393" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F393" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G393" s="1">
-        <v>0</v>
-      </c>
-      <c r="H393" s="2">
-        <v>0</v>
-      </c>
-      <c r="I393" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J393" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A394" s="1">
-        <v>340001</v>
-      </c>
-      <c r="B394" s="1">
-        <v>34</v>
-      </c>
-      <c r="D394" s="1">
-        <v>0</v>
-      </c>
-      <c r="E394" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F394" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G394" s="1">
-        <v>0</v>
-      </c>
-      <c r="H394" s="2">
-        <v>0</v>
-      </c>
-      <c r="I394" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J394" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A395" s="1">
-        <v>350001</v>
-      </c>
-      <c r="B395" s="1">
-        <v>35</v>
-      </c>
-      <c r="D395" s="1">
-        <v>0</v>
-      </c>
-      <c r="E395" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F395" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G395" s="1">
-        <v>0</v>
-      </c>
-      <c r="H395" s="2">
-        <v>0</v>
-      </c>
-      <c r="I395" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J395" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A396" s="1">
-        <v>360001</v>
-      </c>
-      <c r="B396" s="1">
-        <v>36</v>
-      </c>
-      <c r="D396" s="1">
-        <v>0</v>
-      </c>
-      <c r="E396" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F396" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G396" s="1">
-        <v>0</v>
-      </c>
-      <c r="H396" s="2">
-        <v>0</v>
-      </c>
-      <c r="I396" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J396" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A397" s="1">
-        <v>370001</v>
-      </c>
-      <c r="B397" s="1">
-        <v>37</v>
-      </c>
-      <c r="D397" s="1">
-        <v>0</v>
-      </c>
-      <c r="E397" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F397" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G397" s="1">
-        <v>0</v>
-      </c>
-      <c r="H397" s="2">
-        <v>0</v>
-      </c>
-      <c r="I397" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J397" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A398" s="1">
-        <v>380001</v>
-      </c>
-      <c r="B398" s="1">
-        <v>38</v>
-      </c>
-      <c r="D398" s="1">
-        <v>0</v>
-      </c>
-      <c r="E398" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F398" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G398" s="1">
-        <v>0</v>
-      </c>
-      <c r="H398" s="2">
-        <v>0</v>
-      </c>
-      <c r="I398" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J398" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A399" s="1">
-        <v>390001</v>
-      </c>
-      <c r="B399" s="1">
-        <v>39</v>
-      </c>
-      <c r="D399" s="1">
-        <v>0</v>
-      </c>
-      <c r="E399" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F399" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G399" s="1">
-        <v>0</v>
-      </c>
-      <c r="H399" s="2">
-        <v>0</v>
-      </c>
-      <c r="I399" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J399" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A400" s="1">
-        <v>400001</v>
-      </c>
-      <c r="B400" s="1">
-        <v>40</v>
-      </c>
-      <c r="D400" s="1">
-        <v>0</v>
-      </c>
-      <c r="E400" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F400" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G400" s="1">
-        <v>0</v>
-      </c>
-      <c r="H400" s="2">
-        <v>0</v>
-      </c>
-      <c r="I400" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J400" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A401" s="1">
-        <v>410001</v>
-      </c>
-      <c r="B401" s="1">
-        <v>41</v>
-      </c>
-      <c r="D401" s="1">
-        <v>0</v>
-      </c>
-      <c r="E401" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F401" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G401" s="1">
-        <v>0</v>
-      </c>
-      <c r="H401" s="2">
-        <v>0</v>
-      </c>
-      <c r="I401" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J401" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A402" s="1">
-        <v>420001</v>
-      </c>
-      <c r="B402" s="1">
-        <v>42</v>
-      </c>
-      <c r="D402" s="1">
-        <v>0</v>
-      </c>
-      <c r="E402" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F402" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G402" s="1">
-        <v>0</v>
-      </c>
-      <c r="H402" s="2">
-        <v>0</v>
-      </c>
-      <c r="I402" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J402" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A403" s="1">
-        <v>430001</v>
-      </c>
-      <c r="B403" s="1">
-        <v>43</v>
-      </c>
-      <c r="D403" s="1">
-        <v>0</v>
-      </c>
-      <c r="E403" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F403" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G403" s="1">
-        <v>0</v>
-      </c>
-      <c r="H403" s="2">
-        <v>0</v>
-      </c>
-      <c r="I403" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J403" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A404" s="1">
-        <v>440001</v>
-      </c>
-      <c r="B404" s="1">
-        <v>44</v>
-      </c>
-      <c r="D404" s="1">
-        <v>0</v>
-      </c>
-      <c r="E404" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F404" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G404" s="1">
-        <v>0</v>
-      </c>
-      <c r="H404" s="2">
-        <v>0</v>
-      </c>
-      <c r="I404" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J404" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A405" s="1">
-        <v>450001</v>
-      </c>
-      <c r="B405" s="1">
-        <v>45</v>
-      </c>
-      <c r="D405" s="1">
-        <v>0</v>
-      </c>
-      <c r="E405" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F405" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G405" s="1">
-        <v>0</v>
-      </c>
-      <c r="H405" s="2">
-        <v>0</v>
-      </c>
-      <c r="I405" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J405" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A406" s="1">
-        <v>460001</v>
-      </c>
-      <c r="B406" s="1">
-        <v>46</v>
-      </c>
-      <c r="D406" s="1">
-        <v>0</v>
-      </c>
-      <c r="E406" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F406" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G406" s="1">
-        <v>0</v>
-      </c>
-      <c r="H406" s="2">
-        <v>0</v>
-      </c>
-      <c r="I406" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J406" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A407" s="1">
-        <v>470001</v>
-      </c>
-      <c r="B407" s="1">
-        <v>47</v>
-      </c>
-      <c r="D407" s="1">
-        <v>0</v>
-      </c>
-      <c r="E407" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F407" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G407" s="1">
-        <v>0</v>
-      </c>
-      <c r="H407" s="2">
-        <v>0</v>
-      </c>
-      <c r="I407" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J407" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A408" s="1">
-        <v>480001</v>
-      </c>
-      <c r="B408" s="1">
-        <v>48</v>
-      </c>
-      <c r="D408" s="1">
-        <v>0</v>
-      </c>
-      <c r="E408" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F408" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G408" s="1">
-        <v>0</v>
-      </c>
-      <c r="H408" s="2">
-        <v>0</v>
-      </c>
-      <c r="I408" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J408" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A409" s="1">
-        <v>490001</v>
-      </c>
-      <c r="B409" s="1">
-        <v>49</v>
-      </c>
-      <c r="D409" s="1">
-        <v>0</v>
-      </c>
-      <c r="E409" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F409" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G409" s="1">
-        <v>0</v>
-      </c>
-      <c r="H409" s="2">
-        <v>0</v>
-      </c>
-      <c r="I409" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J409" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A410" s="1">
-        <v>500001</v>
-      </c>
-      <c r="B410" s="1">
-        <v>50</v>
-      </c>
-      <c r="D410" s="1">
-        <v>0</v>
-      </c>
-      <c r="E410" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F410" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G410" s="1">
-        <v>0</v>
-      </c>
-      <c r="H410" s="2">
-        <v>0</v>
-      </c>
-      <c r="I410" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J410" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A411" s="1">
-        <v>510001</v>
-      </c>
-      <c r="B411" s="1">
-        <v>51</v>
-      </c>
-      <c r="D411" s="1">
-        <v>0</v>
-      </c>
-      <c r="E411" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F411" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G411" s="1">
-        <v>0</v>
-      </c>
-      <c r="H411" s="2">
-        <v>0</v>
-      </c>
-      <c r="I411" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J411" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A412" s="1">
-        <v>520001</v>
-      </c>
-      <c r="B412" s="1">
-        <v>52</v>
-      </c>
-      <c r="D412" s="1">
-        <v>0</v>
-      </c>
-      <c r="E412" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F412" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G412" s="1">
-        <v>0</v>
-      </c>
-      <c r="H412" s="2">
-        <v>0</v>
-      </c>
-      <c r="I412" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J412" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A413" s="1">
-        <v>530001</v>
-      </c>
-      <c r="B413" s="1">
-        <v>53</v>
-      </c>
-      <c r="D413" s="1">
-        <v>0</v>
-      </c>
-      <c r="E413" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F413" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G413" s="1">
-        <v>0</v>
-      </c>
-      <c r="H413" s="2">
-        <v>0</v>
-      </c>
-      <c r="I413" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J413" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A414" s="1">
-        <v>540001</v>
-      </c>
-      <c r="B414" s="1">
-        <v>54</v>
-      </c>
-      <c r="D414" s="1">
-        <v>0</v>
-      </c>
-      <c r="E414" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F414" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G414" s="1">
-        <v>0</v>
-      </c>
-      <c r="H414" s="2">
-        <v>0</v>
-      </c>
-      <c r="I414" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J414" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A415" s="1">
-        <v>550001</v>
-      </c>
-      <c r="B415" s="1">
-        <v>55</v>
-      </c>
-      <c r="D415" s="1">
-        <v>0</v>
-      </c>
-      <c r="E415" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F415" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G415" s="1">
-        <v>0</v>
-      </c>
-      <c r="H415" s="2">
-        <v>0</v>
-      </c>
-      <c r="I415" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J415" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A416" s="1">
-        <v>560001</v>
-      </c>
-      <c r="B416" s="1">
-        <v>56</v>
-      </c>
-      <c r="D416" s="1">
-        <v>0</v>
-      </c>
-      <c r="E416" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F416" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G416" s="1">
-        <v>0</v>
-      </c>
-      <c r="H416" s="2">
-        <v>0</v>
-      </c>
-      <c r="I416" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J416" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A417" s="1">
-        <v>570001</v>
-      </c>
-      <c r="B417" s="1">
-        <v>57</v>
-      </c>
-      <c r="D417" s="1">
-        <v>0</v>
-      </c>
-      <c r="E417" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F417" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G417" s="1">
-        <v>0</v>
-      </c>
-      <c r="H417" s="2">
-        <v>0</v>
-      </c>
-      <c r="I417" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J417" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A418" s="1">
-        <v>580001</v>
-      </c>
-      <c r="B418" s="1">
-        <v>58</v>
-      </c>
-      <c r="D418" s="1">
-        <v>0</v>
-      </c>
-      <c r="E418" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F418" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G418" s="1">
-        <v>0</v>
-      </c>
-      <c r="H418" s="2">
-        <v>0</v>
-      </c>
-      <c r="I418" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J418" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A419" s="1">
-        <v>590001</v>
-      </c>
-      <c r="B419" s="1">
-        <v>59</v>
-      </c>
-      <c r="D419" s="1">
-        <v>0</v>
-      </c>
-      <c r="E419" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F419" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G419" s="1">
-        <v>0</v>
-      </c>
-      <c r="H419" s="2">
-        <v>0</v>
-      </c>
-      <c r="I419" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J419" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A420" s="1">
-        <v>600001</v>
-      </c>
-      <c r="B420" s="1">
-        <v>60</v>
-      </c>
-      <c r="D420" s="1">
-        <v>0</v>
-      </c>
-      <c r="E420" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F420" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G420" s="1">
-        <v>0</v>
-      </c>
-      <c r="H420" s="2">
-        <v>0</v>
-      </c>
-      <c r="I420" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J420" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A421" s="1">
-        <v>610001</v>
-      </c>
-      <c r="B421" s="1">
-        <v>61</v>
-      </c>
-      <c r="D421" s="1">
-        <v>0</v>
-      </c>
-      <c r="E421" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F421" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G421" s="1">
-        <v>0</v>
-      </c>
-      <c r="H421" s="2">
-        <v>0</v>
-      </c>
-      <c r="I421" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J421" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A422" s="1">
-        <v>620001</v>
-      </c>
-      <c r="B422" s="1">
-        <v>62</v>
-      </c>
-      <c r="D422" s="1">
-        <v>0</v>
-      </c>
-      <c r="E422" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F422" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G422" s="1">
-        <v>0</v>
-      </c>
-      <c r="H422" s="2">
-        <v>0</v>
-      </c>
-      <c r="I422" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J422" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A423" s="1">
-        <v>630001</v>
-      </c>
-      <c r="B423" s="1">
-        <v>63</v>
-      </c>
-      <c r="D423" s="1">
-        <v>0</v>
-      </c>
-      <c r="E423" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F423" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G423" s="1">
-        <v>0</v>
-      </c>
-      <c r="H423" s="2">
-        <v>0</v>
-      </c>
-      <c r="I423" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J423" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A424" s="1">
-        <v>640001</v>
-      </c>
-      <c r="B424" s="1">
-        <v>64</v>
-      </c>
-      <c r="D424" s="1">
-        <v>0</v>
-      </c>
-      <c r="E424" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F424" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G424" s="1">
-        <v>0</v>
-      </c>
-      <c r="H424" s="2">
-        <v>0</v>
-      </c>
-      <c r="I424" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J424" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A425" s="1">
-        <v>650001</v>
-      </c>
-      <c r="B425" s="1">
-        <v>65</v>
-      </c>
-      <c r="D425" s="1">
-        <v>0</v>
-      </c>
-      <c r="E425" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F425" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G425" s="1">
-        <v>0</v>
-      </c>
-      <c r="H425" s="2">
-        <v>0</v>
-      </c>
-      <c r="I425" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J425" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A426" s="1">
-        <v>660001</v>
-      </c>
-      <c r="B426" s="1">
-        <v>66</v>
-      </c>
-      <c r="D426" s="1">
-        <v>0</v>
-      </c>
-      <c r="E426" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F426" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G426" s="1">
-        <v>0</v>
-      </c>
-      <c r="H426" s="2">
-        <v>0</v>
-      </c>
-      <c r="I426" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J426" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A427" s="1">
-        <v>670001</v>
-      </c>
-      <c r="B427" s="1">
-        <v>67</v>
-      </c>
-      <c r="D427" s="1">
-        <v>0</v>
-      </c>
-      <c r="E427" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F427" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G427" s="1">
-        <v>0</v>
-      </c>
-      <c r="H427" s="2">
-        <v>0</v>
-      </c>
-      <c r="I427" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J427" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A428" s="1">
-        <v>680001</v>
-      </c>
-      <c r="B428" s="1">
-        <v>68</v>
-      </c>
-      <c r="D428" s="1">
-        <v>0</v>
-      </c>
-      <c r="E428" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F428" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G428" s="1">
-        <v>0</v>
-      </c>
-      <c r="H428" s="2">
-        <v>0</v>
-      </c>
-      <c r="I428" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J428" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A429" s="1">
-        <v>690001</v>
-      </c>
-      <c r="B429" s="1">
-        <v>69</v>
-      </c>
-      <c r="D429" s="1">
-        <v>0</v>
-      </c>
-      <c r="E429" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F429" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G429" s="1">
-        <v>0</v>
-      </c>
-      <c r="H429" s="2">
-        <v>0</v>
-      </c>
-      <c r="I429" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J429" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A430" s="1">
-        <v>700001</v>
-      </c>
-      <c r="B430" s="1">
-        <v>70</v>
-      </c>
-      <c r="D430" s="1">
-        <v>0</v>
-      </c>
-      <c r="E430" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F430" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G430" s="1">
-        <v>0</v>
-      </c>
-      <c r="H430" s="2">
-        <v>0</v>
-      </c>
-      <c r="I430" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J430" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A431" s="1">
-        <v>710001</v>
-      </c>
-      <c r="B431" s="1">
-        <v>71</v>
-      </c>
-      <c r="D431" s="1">
-        <v>0</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F431" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G431" s="1">
-        <v>0</v>
-      </c>
-      <c r="H431" s="2">
-        <v>0</v>
-      </c>
-      <c r="I431" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J431" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A432" s="1">
-        <v>720001</v>
-      </c>
-      <c r="B432" s="1">
-        <v>72</v>
-      </c>
-      <c r="D432" s="1">
-        <v>0</v>
-      </c>
-      <c r="E432" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F432" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G432" s="1">
-        <v>0</v>
-      </c>
-      <c r="H432" s="2">
-        <v>0</v>
-      </c>
-      <c r="I432" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J432" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A433" s="1">
-        <v>730001</v>
-      </c>
-      <c r="B433" s="1">
-        <v>73</v>
-      </c>
-      <c r="D433" s="1">
-        <v>0</v>
-      </c>
-      <c r="E433" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F433" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G433" s="1">
-        <v>0</v>
-      </c>
-      <c r="H433" s="2">
-        <v>0</v>
-      </c>
-      <c r="I433" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J433" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A434" s="1">
-        <v>740001</v>
-      </c>
-      <c r="B434" s="1">
-        <v>74</v>
-      </c>
-      <c r="D434" s="1">
-        <v>0</v>
-      </c>
-      <c r="E434" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F434" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G434" s="1">
-        <v>0</v>
-      </c>
-      <c r="H434" s="2">
-        <v>0</v>
-      </c>
-      <c r="I434" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J434" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A435" s="1">
-        <v>750001</v>
-      </c>
-      <c r="B435" s="1">
-        <v>75</v>
-      </c>
-      <c r="D435" s="1">
-        <v>0</v>
-      </c>
-      <c r="E435" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F435" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G435" s="1">
-        <v>0</v>
-      </c>
-      <c r="H435" s="2">
-        <v>0</v>
-      </c>
-      <c r="I435" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J435" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A436" s="1">
-        <v>760001</v>
-      </c>
-      <c r="B436" s="1">
-        <v>76</v>
-      </c>
-      <c r="D436" s="1">
-        <v>0</v>
-      </c>
-      <c r="E436" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F436" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G436" s="1">
-        <v>0</v>
-      </c>
-      <c r="H436" s="2">
-        <v>0</v>
-      </c>
-      <c r="I436" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J436" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A437" s="1">
-        <v>770001</v>
-      </c>
-      <c r="B437" s="1">
-        <v>77</v>
-      </c>
-      <c r="D437" s="1">
-        <v>0</v>
-      </c>
-      <c r="E437" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F437" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G437" s="1">
-        <v>0</v>
-      </c>
-      <c r="H437" s="2">
-        <v>0</v>
-      </c>
-      <c r="I437" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J437" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A438" s="1">
-        <v>780001</v>
-      </c>
-      <c r="B438" s="1">
-        <v>78</v>
-      </c>
-      <c r="D438" s="1">
-        <v>0</v>
-      </c>
-      <c r="E438" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F438" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G438" s="1">
-        <v>0</v>
-      </c>
-      <c r="H438" s="2">
-        <v>0</v>
-      </c>
-      <c r="I438" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J438" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A439" s="1">
-        <v>790001</v>
-      </c>
-      <c r="B439" s="1">
-        <v>79</v>
-      </c>
-      <c r="D439" s="1">
-        <v>0</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G439" s="1">
-        <v>0</v>
-      </c>
-      <c r="H439" s="2">
-        <v>0</v>
-      </c>
-      <c r="I439" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J439" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A440" s="1">
-        <v>800001</v>
-      </c>
-      <c r="B440" s="1">
-        <v>80</v>
-      </c>
-      <c r="D440" s="1">
-        <v>0</v>
-      </c>
-      <c r="E440" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F440" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G440" s="1">
-        <v>0</v>
-      </c>
-      <c r="H440" s="2">
-        <v>0</v>
-      </c>
-      <c r="I440" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J440" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A441" s="1">
-        <v>810001</v>
-      </c>
-      <c r="B441" s="1">
-        <v>81</v>
-      </c>
-      <c r="D441" s="1">
-        <v>0</v>
-      </c>
-      <c r="E441" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F441" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G441" s="1">
-        <v>0</v>
-      </c>
-      <c r="H441" s="2">
-        <v>0</v>
-      </c>
-      <c r="I441" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J441" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A442" s="1">
-        <v>820001</v>
-      </c>
-      <c r="B442" s="1">
-        <v>82</v>
-      </c>
-      <c r="D442" s="1">
-        <v>0</v>
-      </c>
-      <c r="E442" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F442" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G442" s="1">
-        <v>0</v>
-      </c>
-      <c r="H442" s="2">
-        <v>0</v>
-      </c>
-      <c r="I442" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J442" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A443" s="1">
-        <v>830001</v>
-      </c>
-      <c r="B443" s="1">
-        <v>83</v>
-      </c>
-      <c r="D443" s="1">
-        <v>0</v>
-      </c>
-      <c r="E443" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F443" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G443" s="1">
-        <v>0</v>
-      </c>
-      <c r="H443" s="2">
-        <v>0</v>
-      </c>
-      <c r="I443" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J443" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A444" s="1">
-        <v>840001</v>
-      </c>
-      <c r="B444" s="1">
-        <v>84</v>
-      </c>
-      <c r="D444" s="1">
-        <v>0</v>
-      </c>
-      <c r="E444" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F444" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G444" s="1">
-        <v>0</v>
-      </c>
-      <c r="H444" s="2">
-        <v>0</v>
-      </c>
-      <c r="I444" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J444" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A445" s="1">
-        <v>850001</v>
-      </c>
-      <c r="B445" s="1">
-        <v>85</v>
-      </c>
-      <c r="D445" s="1">
-        <v>0</v>
-      </c>
-      <c r="E445" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F445" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G445" s="1">
-        <v>0</v>
-      </c>
-      <c r="H445" s="2">
-        <v>0</v>
-      </c>
-      <c r="I445" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J445" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A446" s="1">
-        <v>860001</v>
-      </c>
-      <c r="B446" s="1">
-        <v>86</v>
-      </c>
-      <c r="D446" s="1">
-        <v>0</v>
-      </c>
-      <c r="E446" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F446" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G446" s="1">
-        <v>0</v>
-      </c>
-      <c r="H446" s="2">
-        <v>0</v>
-      </c>
-      <c r="I446" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J446" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A447" s="1">
-        <v>870001</v>
-      </c>
-      <c r="B447" s="1">
-        <v>87</v>
-      </c>
-      <c r="D447" s="1">
-        <v>0</v>
-      </c>
-      <c r="E447" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F447" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G447" s="1">
-        <v>0</v>
-      </c>
-      <c r="H447" s="2">
-        <v>0</v>
-      </c>
-      <c r="I447" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J447" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A448" s="1">
-        <v>880001</v>
-      </c>
-      <c r="B448" s="1">
-        <v>88</v>
-      </c>
-      <c r="D448" s="1">
-        <v>0</v>
-      </c>
-      <c r="E448" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F448" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G448" s="1">
-        <v>0</v>
-      </c>
-      <c r="H448" s="2">
-        <v>0</v>
-      </c>
-      <c r="I448" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J448" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A449" s="1">
-        <v>890001</v>
-      </c>
-      <c r="B449" s="1">
-        <v>89</v>
-      </c>
-      <c r="D449" s="1">
-        <v>0</v>
-      </c>
-      <c r="E449" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F449" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G449" s="1">
-        <v>0</v>
-      </c>
-      <c r="H449" s="2">
-        <v>0</v>
-      </c>
-      <c r="I449" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J449" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A450" s="1">
-        <v>900001</v>
-      </c>
-      <c r="B450" s="1">
-        <v>90</v>
-      </c>
-      <c r="D450" s="1">
-        <v>0</v>
-      </c>
-      <c r="E450" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F450" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G450" s="1">
-        <v>0</v>
-      </c>
-      <c r="H450" s="2">
-        <v>0</v>
-      </c>
-      <c r="I450" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J450" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A451" s="1">
-        <v>910001</v>
-      </c>
-      <c r="B451" s="1">
-        <v>91</v>
-      </c>
-      <c r="D451" s="1">
-        <v>0</v>
-      </c>
-      <c r="E451" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F451" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G451" s="1">
-        <v>0</v>
-      </c>
-      <c r="H451" s="2">
-        <v>0</v>
-      </c>
-      <c r="I451" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J451" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A452" s="1">
-        <v>920001</v>
-      </c>
-      <c r="B452" s="1">
-        <v>92</v>
-      </c>
-      <c r="D452" s="1">
-        <v>0</v>
-      </c>
-      <c r="E452" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F452" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G452" s="1">
-        <v>0</v>
-      </c>
-      <c r="H452" s="2">
-        <v>0</v>
-      </c>
-      <c r="I452" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J452" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A453" s="1">
-        <v>930001</v>
-      </c>
-      <c r="B453" s="1">
-        <v>93</v>
-      </c>
-      <c r="D453" s="1">
-        <v>0</v>
-      </c>
-      <c r="E453" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F453" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G453" s="1">
-        <v>0</v>
-      </c>
-      <c r="H453" s="2">
-        <v>0</v>
-      </c>
-      <c r="I453" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J453" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A454" s="1">
-        <v>940001</v>
-      </c>
-      <c r="B454" s="1">
-        <v>94</v>
-      </c>
-      <c r="D454" s="1">
-        <v>0</v>
-      </c>
-      <c r="E454" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F454" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G454" s="1">
-        <v>0</v>
-      </c>
-      <c r="H454" s="2">
-        <v>0</v>
-      </c>
-      <c r="I454" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J454" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A455" s="1">
-        <v>950001</v>
-      </c>
-      <c r="B455" s="1">
-        <v>95</v>
-      </c>
-      <c r="D455" s="1">
-        <v>0</v>
-      </c>
-      <c r="E455" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F455" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G455" s="1">
-        <v>0</v>
-      </c>
-      <c r="H455" s="2">
-        <v>0</v>
-      </c>
-      <c r="I455" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J455" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A456" s="1">
-        <v>960001</v>
-      </c>
-      <c r="B456" s="1">
-        <v>96</v>
-      </c>
-      <c r="D456" s="1">
-        <v>0</v>
-      </c>
-      <c r="E456" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F456" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G456" s="1">
-        <v>0</v>
-      </c>
-      <c r="H456" s="2">
-        <v>0</v>
-      </c>
-      <c r="I456" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J456" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A457" s="1">
-        <v>970001</v>
-      </c>
-      <c r="B457" s="1">
-        <v>97</v>
-      </c>
-      <c r="D457" s="1">
-        <v>0</v>
-      </c>
-      <c r="E457" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F457" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G457" s="1">
-        <v>0</v>
-      </c>
-      <c r="H457" s="2">
-        <v>0</v>
-      </c>
-      <c r="I457" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J457" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A458" s="1">
-        <v>980001</v>
-      </c>
-      <c r="B458" s="1">
-        <v>98</v>
-      </c>
-      <c r="D458" s="1">
-        <v>0</v>
-      </c>
-      <c r="E458" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F458" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G458" s="1">
-        <v>0</v>
-      </c>
-      <c r="H458" s="2">
-        <v>0</v>
-      </c>
-      <c r="I458" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J458" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A459" s="1">
-        <v>990001</v>
-      </c>
-      <c r="B459" s="1">
-        <v>99</v>
-      </c>
-      <c r="D459" s="1">
-        <v>0</v>
-      </c>
-      <c r="E459" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F459" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G459" s="1">
-        <v>0</v>
-      </c>
-      <c r="H459" s="2">
-        <v>0</v>
-      </c>
-      <c r="I459" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J459" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A460" s="1">
-        <v>1000001</v>
-      </c>
-      <c r="B460" s="1">
-        <v>100</v>
-      </c>
-      <c r="D460" s="1">
-        <v>0</v>
-      </c>
-      <c r="E460" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F460" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G460" s="1">
-        <v>0</v>
-      </c>
-      <c r="H460" s="2">
-        <v>0</v>
-      </c>
-      <c r="I460" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J460" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A461" s="1">
-        <v>1010001</v>
-      </c>
-      <c r="B461" s="1">
-        <v>101</v>
-      </c>
-      <c r="D461" s="1">
-        <v>0</v>
-      </c>
-      <c r="E461" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F461" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G461" s="1">
-        <v>0</v>
-      </c>
-      <c r="H461" s="2">
-        <v>0</v>
-      </c>
-      <c r="I461" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J461" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A462" s="1">
-        <v>1020001</v>
-      </c>
-      <c r="B462" s="1">
-        <v>102</v>
-      </c>
-      <c r="D462" s="1">
-        <v>0</v>
-      </c>
-      <c r="E462" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F462" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G462" s="1">
-        <v>0</v>
-      </c>
-      <c r="H462" s="2">
-        <v>0</v>
-      </c>
-      <c r="I462" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J462" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A463" s="1">
-        <v>1030001</v>
-      </c>
-      <c r="B463" s="1">
-        <v>103</v>
-      </c>
-      <c r="D463" s="1">
-        <v>0</v>
-      </c>
-      <c r="E463" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F463" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G463" s="1">
-        <v>0</v>
-      </c>
-      <c r="H463" s="2">
-        <v>0</v>
-      </c>
-      <c r="I463" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J463" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A464" s="1">
-        <v>1040001</v>
-      </c>
-      <c r="B464" s="1">
-        <v>104</v>
-      </c>
-      <c r="D464" s="1">
-        <v>0</v>
-      </c>
-      <c r="E464" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F464" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G464" s="1">
-        <v>0</v>
-      </c>
-      <c r="H464" s="2">
-        <v>0</v>
-      </c>
-      <c r="I464" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J464" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A465" s="1">
-        <v>1050001</v>
-      </c>
-      <c r="B465" s="1">
-        <v>105</v>
-      </c>
-      <c r="D465" s="1">
-        <v>0</v>
-      </c>
-      <c r="E465" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F465" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G465" s="1">
-        <v>0</v>
-      </c>
-      <c r="H465" s="2">
-        <v>0</v>
-      </c>
-      <c r="I465" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J465" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A466" s="1">
-        <v>1060001</v>
-      </c>
-      <c r="B466" s="1">
-        <v>106</v>
-      </c>
-      <c r="D466" s="1">
-        <v>0</v>
-      </c>
-      <c r="E466" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F466" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G466" s="1">
-        <v>0</v>
-      </c>
-      <c r="H466" s="2">
-        <v>0</v>
-      </c>
-      <c r="I466" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J466" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A467" s="1">
-        <v>1070001</v>
-      </c>
-      <c r="B467" s="1">
-        <v>107</v>
-      </c>
-      <c r="D467" s="1">
-        <v>0</v>
-      </c>
-      <c r="E467" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F467" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G467" s="1">
-        <v>0</v>
-      </c>
-      <c r="H467" s="2">
-        <v>0</v>
-      </c>
-      <c r="I467" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J467" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A468" s="1">
-        <v>1080001</v>
-      </c>
-      <c r="B468" s="1">
-        <v>108</v>
-      </c>
-      <c r="D468" s="1">
-        <v>0</v>
-      </c>
-      <c r="E468" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F468" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G468" s="1">
-        <v>0</v>
-      </c>
-      <c r="H468" s="2">
-        <v>0</v>
-      </c>
-      <c r="I468" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J468" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A469" s="1">
-        <v>1090001</v>
-      </c>
-      <c r="B469" s="1">
-        <v>109</v>
-      </c>
-      <c r="D469" s="1">
-        <v>0</v>
-      </c>
-      <c r="E469" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F469" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G469" s="1">
-        <v>0</v>
-      </c>
-      <c r="H469" s="2">
-        <v>0</v>
-      </c>
-      <c r="I469" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J469" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A470" s="1">
-        <v>1100001</v>
-      </c>
-      <c r="B470" s="1">
-        <v>110</v>
-      </c>
-      <c r="D470" s="1">
-        <v>0</v>
-      </c>
-      <c r="E470" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F470" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G470" s="1">
-        <v>0</v>
-      </c>
-      <c r="H470" s="2">
-        <v>0</v>
-      </c>
-      <c r="I470" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J470" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A471" s="1">
-        <v>1110001</v>
-      </c>
-      <c r="B471" s="1">
-        <v>111</v>
-      </c>
-      <c r="D471" s="1">
-        <v>0</v>
-      </c>
-      <c r="E471" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F471" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G471" s="1">
-        <v>0</v>
-      </c>
-      <c r="H471" s="2">
-        <v>0</v>
-      </c>
-      <c r="I471" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J471" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A472" s="1">
-        <v>1120001</v>
-      </c>
-      <c r="B472" s="1">
-        <v>112</v>
-      </c>
-      <c r="D472" s="1">
-        <v>0</v>
-      </c>
-      <c r="E472" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F472" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G472" s="1">
-        <v>0</v>
-      </c>
-      <c r="H472" s="2">
-        <v>0</v>
-      </c>
-      <c r="I472" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J472" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A473" s="1">
-        <v>1130001</v>
-      </c>
-      <c r="B473" s="1">
-        <v>113</v>
-      </c>
-      <c r="D473" s="1">
-        <v>0</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F473" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G473" s="1">
-        <v>0</v>
-      </c>
-      <c r="H473" s="2">
-        <v>0</v>
-      </c>
-      <c r="I473" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J473" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A474" s="1">
-        <v>1140001</v>
-      </c>
-      <c r="B474" s="1">
-        <v>114</v>
-      </c>
-      <c r="D474" s="1">
-        <v>0</v>
-      </c>
-      <c r="E474" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F474" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G474" s="1">
-        <v>0</v>
-      </c>
-      <c r="H474" s="2">
-        <v>0</v>
-      </c>
-      <c r="I474" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J474" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A475" s="1">
-        <v>1150001</v>
-      </c>
-      <c r="B475" s="1">
-        <v>115</v>
-      </c>
-      <c r="D475" s="1">
-        <v>0</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F475" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G475" s="1">
-        <v>0</v>
-      </c>
-      <c r="H475" s="2">
-        <v>0</v>
-      </c>
-      <c r="I475" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J475" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A476" s="1">
-        <v>1160001</v>
-      </c>
-      <c r="B476" s="1">
-        <v>116</v>
-      </c>
-      <c r="D476" s="1">
-        <v>0</v>
-      </c>
-      <c r="E476" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F476" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G476" s="1">
-        <v>0</v>
-      </c>
-      <c r="H476" s="2">
-        <v>0</v>
-      </c>
-      <c r="I476" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J476" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A477" s="1">
-        <v>1170001</v>
-      </c>
-      <c r="B477" s="1">
-        <v>117</v>
-      </c>
-      <c r="D477" s="1">
-        <v>0</v>
-      </c>
-      <c r="E477" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F477" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G477" s="1">
-        <v>0</v>
-      </c>
-      <c r="H477" s="2">
-        <v>0</v>
-      </c>
-      <c r="I477" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J477" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A478" s="1">
-        <v>1180001</v>
-      </c>
-      <c r="B478" s="1">
-        <v>118</v>
-      </c>
-      <c r="D478" s="1">
-        <v>0</v>
-      </c>
-      <c r="E478" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F478" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G478" s="1">
-        <v>0</v>
-      </c>
-      <c r="H478" s="2">
-        <v>0</v>
-      </c>
-      <c r="I478" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J478" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A479" s="1">
-        <v>1190001</v>
-      </c>
-      <c r="B479" s="1">
-        <v>119</v>
-      </c>
-      <c r="D479" s="1">
-        <v>0</v>
-      </c>
-      <c r="E479" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F479" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G479" s="1">
-        <v>0</v>
-      </c>
-      <c r="H479" s="2">
-        <v>0</v>
-      </c>
-      <c r="I479" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J479" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A480" s="1">
-        <v>1200001</v>
-      </c>
-      <c r="B480" s="1">
-        <v>120</v>
-      </c>
-      <c r="D480" s="1">
-        <v>0</v>
-      </c>
-      <c r="E480" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F480" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G480" s="1">
-        <v>0</v>
-      </c>
-      <c r="H480" s="2">
-        <v>0</v>
-      </c>
-      <c r="I480" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J480" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A481" s="1">
-        <v>1210001</v>
-      </c>
-      <c r="B481" s="1">
-        <v>121</v>
-      </c>
-      <c r="D481" s="1">
-        <v>0</v>
-      </c>
-      <c r="E481" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F481" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G481" s="1">
-        <v>0</v>
-      </c>
-      <c r="H481" s="2">
-        <v>0</v>
-      </c>
-      <c r="I481" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J481" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A482" s="1">
-        <v>1220001</v>
-      </c>
-      <c r="B482" s="1">
-        <v>122</v>
-      </c>
-      <c r="D482" s="1">
-        <v>0</v>
-      </c>
-      <c r="E482" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F482" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G482" s="1">
-        <v>0</v>
-      </c>
-      <c r="H482" s="2">
-        <v>0</v>
-      </c>
-      <c r="I482" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J482" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A483" s="1">
-        <v>1230001</v>
-      </c>
-      <c r="B483" s="1">
-        <v>123</v>
-      </c>
-      <c r="D483" s="1">
-        <v>0</v>
-      </c>
-      <c r="E483" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F483" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G483" s="1">
-        <v>0</v>
-      </c>
-      <c r="H483" s="2">
-        <v>0</v>
-      </c>
-      <c r="I483" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J483" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A484" s="1">
-        <v>1240001</v>
-      </c>
-      <c r="B484" s="1">
-        <v>124</v>
-      </c>
-      <c r="D484" s="1">
-        <v>0</v>
-      </c>
-      <c r="E484" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F484" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G484" s="1">
-        <v>0</v>
-      </c>
-      <c r="H484" s="2">
-        <v>0</v>
-      </c>
-      <c r="I484" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J484" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A485" s="1">
-        <v>1250001</v>
-      </c>
-      <c r="B485" s="1">
-        <v>125</v>
-      </c>
-      <c r="D485" s="1">
-        <v>0</v>
-      </c>
-      <c r="E485" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F485" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G485" s="1">
-        <v>0</v>
-      </c>
-      <c r="H485" s="2">
-        <v>0</v>
-      </c>
-      <c r="I485" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J485" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A486" s="1">
-        <v>1260001</v>
-      </c>
-      <c r="B486" s="1">
-        <v>126</v>
-      </c>
-      <c r="D486" s="1">
-        <v>0</v>
-      </c>
-      <c r="E486" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F486" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G486" s="1">
-        <v>0</v>
-      </c>
-      <c r="H486" s="2">
-        <v>0</v>
-      </c>
-      <c r="I486" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J486" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A487" s="1">
-        <v>1270001</v>
-      </c>
-      <c r="B487" s="1">
-        <v>127</v>
-      </c>
-      <c r="D487" s="1">
-        <v>0</v>
-      </c>
-      <c r="E487" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F487" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G487" s="1">
-        <v>0</v>
-      </c>
-      <c r="H487" s="2">
-        <v>0</v>
-      </c>
-      <c r="I487" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J487" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A488" s="1">
-        <v>1280001</v>
-      </c>
-      <c r="B488" s="1">
-        <v>128</v>
-      </c>
-      <c r="D488" s="1">
-        <v>0</v>
-      </c>
-      <c r="E488" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F488" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G488" s="1">
-        <v>0</v>
-      </c>
-      <c r="H488" s="2">
-        <v>0</v>
-      </c>
-      <c r="I488" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J488" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A489" s="1">
-        <v>1290001</v>
-      </c>
-      <c r="B489" s="1">
-        <v>129</v>
-      </c>
-      <c r="D489" s="1">
-        <v>0</v>
-      </c>
-      <c r="E489" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F489" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G489" s="1">
-        <v>0</v>
-      </c>
-      <c r="H489" s="2">
-        <v>0</v>
-      </c>
-      <c r="I489" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J489" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A490" s="1">
-        <v>1300001</v>
-      </c>
-      <c r="B490" s="1">
-        <v>130</v>
-      </c>
-      <c r="D490" s="1">
-        <v>0</v>
-      </c>
-      <c r="E490" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F490" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G490" s="1">
-        <v>0</v>
-      </c>
-      <c r="H490" s="2">
-        <v>0</v>
-      </c>
-      <c r="I490" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J490" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A491" s="1">
-        <v>1310001</v>
-      </c>
-      <c r="B491" s="1">
-        <v>131</v>
-      </c>
-      <c r="D491" s="1">
-        <v>0</v>
-      </c>
-      <c r="E491" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F491" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G491" s="1">
-        <v>0</v>
-      </c>
-      <c r="H491" s="2">
-        <v>0</v>
-      </c>
-      <c r="I491" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J491" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A492" s="1">
-        <v>1320001</v>
-      </c>
-      <c r="B492" s="1">
-        <v>132</v>
-      </c>
-      <c r="D492" s="1">
-        <v>0</v>
-      </c>
-      <c r="E492" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F492" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G492" s="1">
-        <v>0</v>
-      </c>
-      <c r="H492" s="2">
-        <v>0</v>
-      </c>
-      <c r="I492" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J492" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A493" s="1">
-        <v>1330001</v>
-      </c>
-      <c r="B493" s="1">
-        <v>133</v>
-      </c>
-      <c r="D493" s="1">
-        <v>0</v>
-      </c>
-      <c r="E493" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F493" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G493" s="1">
-        <v>0</v>
-      </c>
-      <c r="H493" s="2">
-        <v>0</v>
-      </c>
-      <c r="I493" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J493" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A494" s="1">
-        <v>1340001</v>
-      </c>
-      <c r="B494" s="1">
-        <v>134</v>
-      </c>
-      <c r="D494" s="1">
-        <v>0</v>
-      </c>
-      <c r="E494" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F494" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G494" s="1">
-        <v>0</v>
-      </c>
-      <c r="H494" s="2">
-        <v>0</v>
-      </c>
-      <c r="I494" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J494" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A495" s="1">
-        <v>1350001</v>
-      </c>
-      <c r="B495" s="1">
-        <v>135</v>
-      </c>
-      <c r="D495" s="1">
-        <v>0</v>
-      </c>
-      <c r="E495" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F495" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G495" s="1">
-        <v>0</v>
-      </c>
-      <c r="H495" s="2">
-        <v>0</v>
-      </c>
-      <c r="I495" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J495" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A496" s="1">
-        <v>1360001</v>
-      </c>
-      <c r="B496" s="1">
-        <v>136</v>
-      </c>
-      <c r="D496" s="1">
-        <v>0</v>
-      </c>
-      <c r="E496" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F496" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G496" s="1">
-        <v>0</v>
-      </c>
-      <c r="H496" s="2">
-        <v>0</v>
-      </c>
-      <c r="I496" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J496" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A497" s="1">
-        <v>1370001</v>
-      </c>
-      <c r="B497" s="1">
-        <v>137</v>
-      </c>
-      <c r="D497" s="1">
-        <v>0</v>
-      </c>
-      <c r="E497" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F497" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G497" s="1">
-        <v>0</v>
-      </c>
-      <c r="H497" s="2">
-        <v>0</v>
-      </c>
-      <c r="I497" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J497" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A498" s="1">
-        <v>1380001</v>
-      </c>
-      <c r="B498" s="1">
-        <v>138</v>
-      </c>
-      <c r="D498" s="1">
-        <v>0</v>
-      </c>
-      <c r="E498" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F498" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G498" s="1">
-        <v>0</v>
-      </c>
-      <c r="H498" s="2">
-        <v>0</v>
-      </c>
-      <c r="I498" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J498" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A499" s="1">
-        <v>1390001</v>
-      </c>
-      <c r="B499" s="1">
-        <v>139</v>
-      </c>
-      <c r="D499" s="1">
-        <v>0</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G499" s="1">
-        <v>0</v>
-      </c>
-      <c r="H499" s="2">
-        <v>0</v>
-      </c>
-      <c r="I499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J499" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A500" s="1">
-        <v>1400001</v>
-      </c>
-      <c r="B500" s="1">
-        <v>140</v>
-      </c>
-      <c r="D500" s="1">
-        <v>0</v>
-      </c>
-      <c r="E500" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F500" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G500" s="1">
-        <v>0</v>
-      </c>
-      <c r="H500" s="2">
-        <v>0</v>
-      </c>
-      <c r="I500" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J500" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A501" s="1">
-        <v>1410001</v>
-      </c>
-      <c r="B501" s="1">
-        <v>141</v>
-      </c>
-      <c r="D501" s="1">
-        <v>0</v>
-      </c>
-      <c r="E501" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F501" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G501" s="1">
-        <v>0</v>
-      </c>
-      <c r="H501" s="2">
-        <v>0</v>
-      </c>
-      <c r="I501" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J501" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A502" s="1">
-        <v>1420001</v>
-      </c>
-      <c r="B502" s="1">
-        <v>142</v>
-      </c>
-      <c r="D502" s="1">
-        <v>0</v>
-      </c>
-      <c r="E502" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F502" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G502" s="1">
-        <v>0</v>
-      </c>
-      <c r="H502" s="2">
-        <v>0</v>
-      </c>
-      <c r="I502" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J502" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A503" s="1">
-        <v>1430001</v>
-      </c>
-      <c r="B503" s="1">
-        <v>143</v>
-      </c>
-      <c r="D503" s="1">
-        <v>0</v>
-      </c>
-      <c r="E503" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F503" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G503" s="1">
-        <v>0</v>
-      </c>
-      <c r="H503" s="2">
-        <v>0</v>
-      </c>
-      <c r="I503" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J503" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A504" s="1">
-        <v>1440001</v>
-      </c>
-      <c r="B504" s="1">
-        <v>144</v>
-      </c>
-      <c r="D504" s="1">
-        <v>0</v>
-      </c>
-      <c r="E504" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F504" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G504" s="1">
-        <v>0</v>
-      </c>
-      <c r="H504" s="2">
-        <v>0</v>
-      </c>
-      <c r="I504" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J504" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A505" s="1">
-        <v>1450001</v>
-      </c>
-      <c r="B505" s="1">
-        <v>145</v>
-      </c>
-      <c r="D505" s="1">
-        <v>0</v>
-      </c>
-      <c r="E505" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F505" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G505" s="1">
-        <v>0</v>
-      </c>
-      <c r="H505" s="2">
-        <v>0</v>
-      </c>
-      <c r="I505" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J505" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A506" s="1">
-        <v>1460001</v>
-      </c>
-      <c r="B506" s="1">
-        <v>146</v>
-      </c>
-      <c r="D506" s="1">
-        <v>0</v>
-      </c>
-      <c r="E506" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F506" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G506" s="1">
-        <v>0</v>
-      </c>
-      <c r="H506" s="2">
-        <v>0</v>
-      </c>
-      <c r="I506" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J506" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A507" s="1">
-        <v>1470001</v>
-      </c>
-      <c r="B507" s="1">
-        <v>147</v>
-      </c>
-      <c r="D507" s="1">
-        <v>0</v>
-      </c>
-      <c r="E507" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F507" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G507" s="1">
-        <v>0</v>
-      </c>
-      <c r="H507" s="2">
-        <v>0</v>
-      </c>
-      <c r="I507" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J507" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A508" s="1">
-        <v>1480001</v>
-      </c>
-      <c r="B508" s="1">
-        <v>148</v>
-      </c>
-      <c r="D508" s="1">
-        <v>0</v>
-      </c>
-      <c r="E508" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F508" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G508" s="1">
-        <v>0</v>
-      </c>
-      <c r="H508" s="2">
-        <v>0</v>
-      </c>
-      <c r="I508" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J508" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A509" s="1">
-        <v>1490001</v>
-      </c>
-      <c r="B509" s="1">
-        <v>149</v>
-      </c>
-      <c r="D509" s="1">
-        <v>0</v>
-      </c>
-      <c r="E509" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F509" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G509" s="1">
-        <v>0</v>
-      </c>
-      <c r="H509" s="2">
-        <v>0</v>
-      </c>
-      <c r="I509" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J509" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A510" s="1">
-        <v>1500001</v>
-      </c>
-      <c r="B510" s="1">
-        <v>150</v>
-      </c>
-      <c r="D510" s="1">
-        <v>0</v>
-      </c>
-      <c r="E510" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F510" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G510" s="1">
-        <v>0</v>
-      </c>
-      <c r="H510" s="2">
-        <v>0</v>
-      </c>
-      <c r="I510" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J510" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A511" s="1">
-        <v>1510001</v>
-      </c>
-      <c r="B511" s="1">
-        <v>151</v>
-      </c>
-      <c r="D511" s="1">
-        <v>0</v>
-      </c>
-      <c r="E511" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F511" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G511" s="1">
-        <v>0</v>
-      </c>
-      <c r="H511" s="2">
-        <v>0</v>
-      </c>
-      <c r="I511" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J511" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A512" s="1">
-        <v>1520001</v>
-      </c>
-      <c r="B512" s="1">
-        <v>152</v>
-      </c>
-      <c r="D512" s="1">
-        <v>0</v>
-      </c>
-      <c r="E512" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F512" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G512" s="1">
-        <v>0</v>
-      </c>
-      <c r="H512" s="2">
-        <v>0</v>
-      </c>
-      <c r="I512" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J512" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A513" s="1">
-        <v>1530001</v>
-      </c>
-      <c r="B513" s="1">
-        <v>153</v>
-      </c>
-      <c r="D513" s="1">
-        <v>0</v>
-      </c>
-      <c r="E513" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F513" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G513" s="1">
-        <v>0</v>
-      </c>
-      <c r="H513" s="2">
-        <v>0</v>
-      </c>
-      <c r="I513" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J513" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A514" s="1">
-        <v>1540001</v>
-      </c>
-      <c r="B514" s="1">
-        <v>154</v>
-      </c>
-      <c r="D514" s="1">
-        <v>0</v>
-      </c>
-      <c r="E514" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F514" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G514" s="1">
-        <v>0</v>
-      </c>
-      <c r="H514" s="2">
-        <v>0</v>
-      </c>
-      <c r="I514" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J514" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A515" s="1">
-        <v>1550001</v>
-      </c>
-      <c r="B515" s="1">
-        <v>155</v>
-      </c>
-      <c r="D515" s="1">
-        <v>0</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G515" s="1">
-        <v>0</v>
-      </c>
-      <c r="H515" s="2">
-        <v>0</v>
-      </c>
-      <c r="I515" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J515" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A516" s="1">
-        <v>1560001</v>
-      </c>
-      <c r="B516" s="1">
-        <v>156</v>
-      </c>
-      <c r="D516" s="1">
-        <v>0</v>
-      </c>
-      <c r="E516" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F516" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G516" s="1">
-        <v>0</v>
-      </c>
-      <c r="H516" s="2">
-        <v>0</v>
-      </c>
-      <c r="I516" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J516" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A517" s="1">
-        <v>1570001</v>
-      </c>
-      <c r="B517" s="1">
-        <v>157</v>
-      </c>
-      <c r="D517" s="1">
-        <v>0</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G517" s="1">
-        <v>0</v>
-      </c>
-      <c r="H517" s="2">
-        <v>0</v>
-      </c>
-      <c r="I517" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J517" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A518" s="1">
-        <v>1580001</v>
-      </c>
-      <c r="B518" s="1">
-        <v>158</v>
-      </c>
-      <c r="D518" s="1">
-        <v>0</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F518" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G518" s="1">
-        <v>0</v>
-      </c>
-      <c r="H518" s="2">
-        <v>0</v>
-      </c>
-      <c r="I518" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J518" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A519" s="1">
-        <v>1590001</v>
-      </c>
-      <c r="B519" s="1">
-        <v>159</v>
-      </c>
-      <c r="D519" s="1">
-        <v>0</v>
-      </c>
-      <c r="E519" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G519" s="1">
-        <v>0</v>
-      </c>
-      <c r="H519" s="2">
-        <v>0</v>
-      </c>
-      <c r="I519" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J519" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A520" s="1">
-        <v>1600001</v>
-      </c>
-      <c r="B520" s="1">
-        <v>160</v>
-      </c>
-      <c r="D520" s="1">
-        <v>0</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G520" s="1">
-        <v>0</v>
-      </c>
-      <c r="H520" s="2">
-        <v>0</v>
-      </c>
-      <c r="I520" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J520" s="4" t="s">
         <v>18</v>
       </c>
     </row>
